--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="F2" t="n">
         <v>-620000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J2" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="K2" t="n">
-        <v>-13445193.69528329</v>
+        <v>-12995348.6958937</v>
       </c>
       <c r="L2" t="n">
-        <v>7262179.996653151</v>
+        <v>6812334.997263561</v>
       </c>
       <c r="M2" t="n">
-        <v>-13445193.69528329</v>
+        <v>-12995348.6958937</v>
       </c>
       <c r="N2" t="n">
-        <v>7262179.996653151</v>
+        <v>6812334.997263561</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="F3" t="n">
         <v>-62000000</v>
       </c>
       <c r="G3" t="n">
-        <v>1036764849.6</v>
+        <v>923715944.4299999</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J3" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="K3" t="n">
-        <v>8935344.454666667</v>
+        <v>7899062.823941666</v>
       </c>
       <c r="L3" t="n">
-        <v>-9503677.788000001</v>
+        <v>-8467396.157274999</v>
       </c>
       <c r="M3" t="n">
-        <v>8114535.354210047</v>
+        <v>7078253.723485045</v>
       </c>
       <c r="N3" t="n">
-        <v>-8682868.687543381</v>
+        <v>-7646587.056818378</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J4" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K4" t="n">
-        <v>7266542.022500001</v>
+        <v>7092348.343916668</v>
       </c>
       <c r="L4" t="n">
-        <v>-7266542.022500001</v>
+        <v>-7092348.343916668</v>
       </c>
       <c r="M4" t="n">
-        <v>6842085.743961188</v>
+        <v>6667892.065377855</v>
       </c>
       <c r="N4" t="n">
-        <v>-6842085.743961188</v>
+        <v>-6667892.065377855</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="F5" t="n">
         <v>-124000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1129206416.05</v>
+        <v>1114570715.1</v>
       </c>
       <c r="H5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J5" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="K5" t="n">
-        <v>7539048.120375002</v>
+        <v>7429280.363250002</v>
       </c>
       <c r="L5" t="n">
-        <v>-8469048.120375002</v>
+        <v>-8359280.363250002</v>
       </c>
       <c r="M5" t="n">
-        <v>6561701.462840755</v>
+        <v>6451933.705715755</v>
       </c>
       <c r="N5" t="n">
-        <v>-7491701.462840755</v>
+        <v>-7381933.705715755</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="F6" t="n">
         <v>-62000000</v>
       </c>
       <c r="G6" t="n">
-        <v>-181337598.87</v>
+        <v>-189621108.9</v>
       </c>
       <c r="H6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J6" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="K6" t="n">
-        <v>-1622250.659133334</v>
+        <v>-1677474.059333334</v>
       </c>
       <c r="L6" t="n">
-        <v>1208917.3258</v>
+        <v>1264140.726</v>
       </c>
       <c r="M6" t="n">
-        <v>-2221922.549544293</v>
+        <v>-2277145.949744293</v>
       </c>
       <c r="N6" t="n">
-        <v>1808589.216210959</v>
+        <v>1863812.616410959</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="F7" t="n">
         <v>-62000000</v>
       </c>
       <c r="G7" t="n">
-        <v>-179428019.53</v>
+        <v>-190737100.49</v>
       </c>
       <c r="H7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J7" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="K7" t="n">
-        <v>-1408330.113925</v>
+        <v>-1474299.752858333</v>
       </c>
       <c r="L7" t="n">
-        <v>1046663.447258333</v>
+        <v>1112633.086191666</v>
       </c>
       <c r="M7" t="n">
-        <v>-1933175.250911301</v>
+        <v>-1999144.889844634</v>
       </c>
       <c r="N7" t="n">
-        <v>1571508.584244634</v>
+        <v>1637478.223177968</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="F8" t="n">
         <v>-31000000</v>
       </c>
       <c r="G8" t="n">
-        <v>180216557.22</v>
+        <v>428219075.5699999</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J8" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="K8" t="n">
-        <v>746082.7861000001</v>
+        <v>1986095.37785</v>
       </c>
       <c r="L8" t="n">
-        <v>-901082.7861000001</v>
+        <v>-2141095.37785</v>
       </c>
       <c r="M8" t="n">
-        <v>296239.7450041097</v>
+        <v>1536252.336754109</v>
       </c>
       <c r="N8" t="n">
-        <v>-451239.7450041097</v>
+        <v>-1691252.336754109</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="F9" t="n">
         <v>-31000000</v>
       </c>
       <c r="G9" t="n">
-        <v>147432754.21</v>
+        <v>-156307218.49</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J9" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="K9" t="n">
-        <v>485136.4758750001</v>
+        <v>-780446.7437083333</v>
       </c>
       <c r="L9" t="n">
-        <v>-614303.1425416667</v>
+        <v>651280.0770416667</v>
       </c>
       <c r="M9" t="n">
-        <v>494511.4758750001</v>
+        <v>-771071.7437083333</v>
       </c>
       <c r="N9" t="n">
-        <v>-623678.1425416667</v>
+        <v>641905.0770416667</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="F10" t="n">
         <v>-31000000</v>
       </c>
       <c r="G10" t="n">
-        <v>9978227.919999994</v>
+        <v>11392415.84999999</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J10" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-70072.57360000003</v>
+        <v>-65358.61383333337</v>
       </c>
       <c r="L10" t="n">
-        <v>-33260.75973333332</v>
+        <v>-37974.71949999998</v>
       </c>
       <c r="M10" t="n">
-        <v>-62572.57360000003</v>
+        <v>-57858.61383333337</v>
       </c>
       <c r="N10" t="n">
-        <v>-40760.75973333332</v>
+        <v>-45474.71949999998</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="F11" t="n">
         <v>-31000000</v>
       </c>
       <c r="G11" t="n">
-        <v>11974398.32</v>
+        <v>15025197.6</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J11" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="K11" t="n">
-        <v>-47564.0042</v>
+        <v>-39937.00599999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-29935.9958</v>
+        <v>-37562.99400000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-41939.0042</v>
+        <v>-34312.00599999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-35560.9958</v>
+        <v>-43187.99400000001</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="F12" t="n">
         <v>-31000000</v>
       </c>
       <c r="G12" t="n">
-        <v>132044465.29</v>
+        <v>26786789.9</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J12" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="K12" t="n">
-        <v>168407.44215</v>
+        <v>-7022.016833333335</v>
       </c>
       <c r="L12" t="n">
-        <v>-220074.1088166667</v>
+        <v>-44644.64983333332</v>
       </c>
       <c r="M12" t="n">
-        <v>172157.44215</v>
+        <v>-3272.016833333335</v>
       </c>
       <c r="N12" t="n">
-        <v>-223824.1088166667</v>
+        <v>-48394.64983333332</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J13" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K13" t="n">
-        <v>28576.68173333334</v>
+        <v>28800.66368333335</v>
       </c>
       <c r="L13" t="n">
-        <v>-28576.68173333334</v>
+        <v>-28800.66368333335</v>
       </c>
       <c r="M13" t="n">
-        <v>30461.95570593608</v>
+        <v>30685.93765593609</v>
       </c>
       <c r="N13" t="n">
-        <v>-30461.95570593608</v>
+        <v>-30685.93765593609</v>
       </c>
     </row>
     <row r="14">
@@ -1087,34 +1087,34 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="F14" t="n">
         <v>-62000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-14962502.42</v>
+        <v>129606409.5</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J14" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>-0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8575726.937258381</v>
+        <v>7395700.684181305</v>
       </c>
       <c r="C2" t="n">
-        <v>-17548740.63588852</v>
+        <v>-16368714.38281144</v>
       </c>
       <c r="D2" t="n">
-        <v>4806890.106208154</v>
+        <v>3626863.853131076</v>
       </c>
       <c r="E2" t="n">
-        <v>-13779903.80483829</v>
+        <v>-12599877.55176121</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-44845718.98</v>
+        <v>-45010257.53</v>
       </c>
       <c r="D2" t="n">
-        <v>-70005305.2013637</v>
+        <v>-70107770.4116428</v>
       </c>
       <c r="E2" t="n">
-        <v>-114851024.1813637</v>
+        <v>-115118027.9416428</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64383203.57</v>
+        <v>74990879.70999999</v>
       </c>
       <c r="D3" t="n">
-        <v>9175112.345246576</v>
+        <v>7822827.81230137</v>
       </c>
       <c r="E3" t="n">
-        <v>73558315.91524658</v>
+        <v>82813707.52230138</v>
       </c>
     </row>
     <row r="4">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>519433585.1</v>
+        <v>518396088.04</v>
       </c>
       <c r="D5" t="n">
-        <v>47471274.13383399</v>
+        <v>47983973.33008273</v>
       </c>
       <c r="E5" t="n">
-        <v>566904859.233834</v>
+        <v>566380061.3700827</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>542295370.39</v>
+        <v>551701010.92</v>
       </c>
       <c r="C2" t="n">
-        <v>-13358918.72228313</v>
+        <v>-14300969.26925871</v>
       </c>
       <c r="D2" t="n">
-        <v>528936451.6677169</v>
+        <v>537400041.6507413</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K2" t="n">
         <v>-620000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="M2" t="n">
         <v>0.03432749872940843</v>
@@ -1510,10 +1510,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="P2" t="n">
-        <v>-33619463.21620177</v>
+        <v>-32494633.94614996</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33619463.21620177</v>
+        <v>-32494633.94614996</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J3" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K3" t="n">
         <v>-62000000</v>
       </c>
       <c r="L3" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="M3" t="n">
         <v>0.03782665436246635</v>
@@ -1571,10 +1571,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="P3" t="n">
-        <v>20372203.03130213</v>
+        <v>17770533.45230579</v>
       </c>
       <c r="Q3" t="n">
-        <v>10186101.51565107</v>
+        <v>8885266.726152895</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J4" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M4" t="n">
         <v>0.03830470017405307</v>
@@ -1632,10 +1632,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="P4" t="n">
-        <v>17251109.82916852</v>
+        <v>16811911.25825904</v>
       </c>
       <c r="Q4" t="n">
-        <v>8625554.914584262</v>
+        <v>8405955.629129518</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J5" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K5" t="n">
         <v>-124000000</v>
       </c>
       <c r="L5" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="M5" t="n">
         <v>0.03852218097221538</v>
@@ -1693,10 +1693,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="P5" t="n">
-        <v>16614400.89951043</v>
+        <v>16336466.04784997</v>
       </c>
       <c r="Q5" t="n">
-        <v>8307200.449755214</v>
+        <v>8168233.023924986</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J6" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K6" t="n">
         <v>-62000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="M6" t="n">
         <v>0.03873510939427094</v>
@@ -1754,10 +1754,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="P6" t="n">
-        <v>-5650065.696432507</v>
+        <v>-5790491.76086683</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5650065.696432507</v>
+        <v>-5790491.76086683</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J7" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K7" t="n">
         <v>-62000000</v>
       </c>
       <c r="L7" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="M7" t="n">
         <v>0.03888939094511485</v>
@@ -1815,10 +1815,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="P7" t="n">
-        <v>-4936984.056458791</v>
+        <v>-5105458.722928206</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4936984.056458791</v>
+        <v>-5105458.722928206</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J8" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K8" t="n">
         <v>-31000000</v>
       </c>
       <c r="L8" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="M8" t="n">
         <v>0.03901400018340251</v>
@@ -1876,10 +1876,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="P8" t="n">
-        <v>759788.3394733594</v>
+        <v>3940141.833224572</v>
       </c>
       <c r="Q8" t="n">
-        <v>379894.1697366797</v>
+        <v>1970070.916612286</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I9" t="n">
         <v>2250000</v>
       </c>
       <c r="J9" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K9" t="n">
         <v>-31000000</v>
       </c>
       <c r="L9" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="M9" t="n">
         <v>0.03908855826627113</v>
@@ -1937,10 +1937,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="P9" t="n">
-        <v>1273776.841778861</v>
+        <v>-1986148.711206025</v>
       </c>
       <c r="Q9" t="n">
-        <v>636888.4208894307</v>
+        <v>-1986148.711206025</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I10" t="n">
         <v>2250000</v>
       </c>
       <c r="J10" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K10" t="n">
         <v>-31000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="M10" t="n">
         <v>0.03915884386251234</v>
@@ -1998,10 +1998,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="P10" t="n">
-        <v>-161860.997434103</v>
+        <v>-149667.0570893367</v>
       </c>
       <c r="Q10" t="n">
-        <v>-161860.997434103</v>
+        <v>-149667.0570893367</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I11" t="n">
         <v>2250000</v>
       </c>
       <c r="J11" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K11" t="n">
         <v>-31000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="M11" t="n">
         <v>0.03922681220647117</v>
@@ -2059,10 +2059,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="P11" t="n">
-        <v>-108951.261100436</v>
+        <v>-89137.46036406193</v>
       </c>
       <c r="Q11" t="n">
-        <v>-108951.261100436</v>
+        <v>-89137.46036406193</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I12" t="n">
         <v>2250000</v>
       </c>
       <c r="J12" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K12" t="n">
         <v>-31000000</v>
       </c>
       <c r="L12" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="M12" t="n">
         <v>0.03929424848359133</v>
@@ -2120,10 +2120,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="P12" t="n">
-        <v>449150.7134622567</v>
+        <v>-8536.538861164656</v>
       </c>
       <c r="Q12" t="n">
-        <v>224575.3567311283</v>
+        <v>-8536.538861164656</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J13" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M13" t="n">
         <v>0.03936107056455495</v>
@@ -2181,10 +2181,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="P13" t="n">
-        <v>79813.76476863457</v>
+        <v>80400.62277743395</v>
       </c>
       <c r="Q13" t="n">
-        <v>39906.88238431729</v>
+        <v>40200.31138871697</v>
       </c>
     </row>
     <row r="14">
@@ -2218,19 +2218,19 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J14" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K14" t="n">
         <v>-62000000</v>
       </c>
       <c r="L14" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="M14" t="n">
         <v>0.03942868733737526</v>
@@ -2242,10 +2242,10 @@
         <v>0.02631330603469872</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K15" t="n">
         <v>-620000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="M15" t="n">
         <v>0.03432749872940843</v>
@@ -2303,10 +2303,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="P15" t="n">
-        <v>18155449.10923949</v>
+        <v>17030836.66542407</v>
       </c>
       <c r="Q15" t="n">
-        <v>9077724.554619746</v>
+        <v>8515418.332712036</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J16" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K16" t="n">
         <v>-62000000</v>
       </c>
       <c r="L16" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="M16" t="n">
         <v>0.03782665436246635</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="P16" t="n">
-        <v>-21752107.73062747</v>
+        <v>-19156040.63783142</v>
       </c>
       <c r="Q16" t="n">
-        <v>-21752107.73062747</v>
+        <v>-19156040.63783142</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J17" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M17" t="n">
         <v>0.03830470017405307</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="P17" t="n">
-        <v>-17177789.11593881</v>
+        <v>-16740457.22797247</v>
       </c>
       <c r="Q17" t="n">
-        <v>-17177789.11593881</v>
+        <v>-16740457.22797247</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I18" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J18" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K18" t="n">
         <v>-124000000</v>
       </c>
       <c r="L18" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="M18" t="n">
         <v>0.03852218097221538</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="P18" t="n">
-        <v>-18850320.29942011</v>
+        <v>-18574127.0487122</v>
       </c>
       <c r="Q18" t="n">
-        <v>-18850320.29942011</v>
+        <v>-18574127.0487122</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I19" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J19" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K19" t="n">
         <v>-62000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="M19" t="n">
         <v>0.03873510939427094</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="P19" t="n">
-        <v>4560797.445338016</v>
+        <v>4700056.675846255</v>
       </c>
       <c r="Q19" t="n">
-        <v>2280398.722669008</v>
+        <v>2350028.337923128</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I20" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J20" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K20" t="n">
         <v>-62000000</v>
       </c>
       <c r="L20" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="M20" t="n">
         <v>0.03888939094511485</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="P20" t="n">
-        <v>3971656.619974947</v>
+        <v>4138380.973767051</v>
       </c>
       <c r="Q20" t="n">
-        <v>1985828.309987474</v>
+        <v>2069190.486883525</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J21" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K21" t="n">
         <v>-31000000</v>
       </c>
       <c r="L21" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="M21" t="n">
         <v>0.03901400018340251</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="P21" t="n">
-        <v>-1142940.962393563</v>
+        <v>-4283757.348108819</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1142940.962393563</v>
+        <v>-4283757.348108819</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I22" t="n">
         <v>2250000</v>
       </c>
       <c r="J22" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K22" t="n">
         <v>-31000000</v>
       </c>
       <c r="L22" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="M22" t="n">
         <v>0.03908855826627113</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="P22" t="n">
-        <v>-1583121.729995623</v>
+        <v>1629388.312243579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1583121.729995623</v>
+        <v>814694.1561217897</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I23" t="n">
         <v>2250000</v>
       </c>
       <c r="J23" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K23" t="n">
         <v>-31000000</v>
       </c>
       <c r="L23" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="M23" t="n">
         <v>0.03915884386251234</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="P23" t="n">
-        <v>-103695.1061662082</v>
+        <v>-115687.3889809956</v>
       </c>
       <c r="Q23" t="n">
-        <v>-103695.1061662082</v>
+        <v>-115687.3889809956</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I24" t="n">
         <v>2250000</v>
       </c>
       <c r="J24" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K24" t="n">
         <v>-31000000</v>
       </c>
       <c r="L24" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="M24" t="n">
         <v>0.03922681220647117</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="P24" t="n">
-        <v>-90664.62000731099</v>
+        <v>-110110.0511051501</v>
       </c>
       <c r="Q24" t="n">
-        <v>-90664.62000731099</v>
+        <v>-110110.0511051501</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I25" t="n">
         <v>2250000</v>
       </c>
       <c r="J25" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K25" t="n">
         <v>-31000000</v>
       </c>
       <c r="L25" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="M25" t="n">
         <v>0.03929424848359133</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="P25" t="n">
-        <v>-571903.5352837283</v>
+        <v>-123655.4519297632</v>
       </c>
       <c r="Q25" t="n">
-        <v>-571903.5352837283</v>
+        <v>-123655.4519297632</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J26" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M26" t="n">
         <v>0.03936107056455495</v>
@@ -2974,10 +2974,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="P26" t="n">
-        <v>-78005.30013467018</v>
+        <v>-78578.86078859412</v>
       </c>
       <c r="Q26" t="n">
-        <v>-78005.30013467018</v>
+        <v>-78578.86078859412</v>
       </c>
     </row>
     <row r="27">
@@ -3011,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J27" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K27" t="n">
         <v>-62000000</v>
       </c>
       <c r="L27" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="M27" t="n">
         <v>0.03942868733737526</v>
@@ -3035,10 +3035,10 @@
         <v>-0.02566354060598441</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K28" t="n">
         <v>-620000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="M28" t="n">
         <v>0.03432749872940843</v>
@@ -3096,10 +3096,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="P28" t="n">
-        <v>16448367.26309286</v>
+        <v>15429497.47952432</v>
       </c>
       <c r="Q28" t="n">
-        <v>8224183.631546429</v>
+        <v>7714748.739762162</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J29" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K29" t="n">
         <v>-62000000</v>
       </c>
       <c r="L29" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="M29" t="n">
         <v>0.03782665436246635</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="P29" t="n">
-        <v>-17243095.31853269</v>
+        <v>-15185169.12173664</v>
       </c>
       <c r="Q29" t="n">
-        <v>-17243095.31853269</v>
+        <v>-15185169.12173664</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J30" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M30" t="n">
         <v>0.03830470017405307</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="P30" t="n">
-        <v>-11783962.85166252</v>
+        <v>-11483953.18878565</v>
       </c>
       <c r="Q30" t="n">
-        <v>-11783962.85166252</v>
+        <v>-11483953.18878565</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I31" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J31" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K31" t="n">
         <v>-124000000</v>
       </c>
       <c r="L31" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="M31" t="n">
         <v>0.03852218097221538</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="P31" t="n">
-        <v>-11110160.42325164</v>
+        <v>-10947375.32069406</v>
       </c>
       <c r="Q31" t="n">
-        <v>-11110160.42325164</v>
+        <v>-10947375.32069406</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I32" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J32" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K32" t="n">
         <v>-62000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="M32" t="n">
         <v>0.03873510939427094</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="P32" t="n">
-        <v>2279755.412571813</v>
+        <v>2349365.385017809</v>
       </c>
       <c r="Q32" t="n">
-        <v>1139877.706285907</v>
+        <v>1174682.692508904</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I33" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J33" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K33" t="n">
         <v>-62000000</v>
       </c>
       <c r="L33" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="M33" t="n">
         <v>0.03888939094511485</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="P33" t="n">
-        <v>1655415.669220475</v>
+        <v>1724907.605235288</v>
       </c>
       <c r="Q33" t="n">
-        <v>827707.8346102377</v>
+        <v>862453.8026176442</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J34" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K34" t="n">
         <v>-31000000</v>
       </c>
       <c r="L34" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="M34" t="n">
         <v>0.03901400018340251</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="P34" t="n">
-        <v>-389461.4875674455</v>
+        <v>-1459706.637583918</v>
       </c>
       <c r="Q34" t="n">
-        <v>-389461.4875674455</v>
+        <v>-1459706.637583918</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I35" t="n">
         <v>2250000</v>
       </c>
       <c r="J35" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K35" t="n">
         <v>-31000000</v>
       </c>
       <c r="L35" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="M35" t="n">
         <v>0.03908855826627113</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="P35" t="n">
-        <v>-427254.1593008393</v>
+        <v>439740.6215403088</v>
       </c>
       <c r="Q35" t="n">
-        <v>-427254.1593008393</v>
+        <v>219870.3107701544</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I36" t="n">
         <v>2250000</v>
       </c>
       <c r="J36" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K36" t="n">
         <v>-31000000</v>
       </c>
       <c r="L36" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="M36" t="n">
         <v>0.03915884386251234</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="P36" t="n">
-        <v>-21333.04469574491</v>
+        <v>-23800.19975011954</v>
       </c>
       <c r="Q36" t="n">
-        <v>-21333.04469574491</v>
+        <v>-23800.19975011954</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I37" t="n">
         <v>2250000</v>
       </c>
       <c r="J37" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K37" t="n">
         <v>-31000000</v>
       </c>
       <c r="L37" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="M37" t="n">
         <v>0.03922681220647117</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="P37" t="n">
-        <v>-13234.56092839752</v>
+        <v>-16073.06334116399</v>
       </c>
       <c r="Q37" t="n">
-        <v>-13234.56092839752</v>
+        <v>-16073.06334116399</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I38" t="n">
         <v>2250000</v>
       </c>
       <c r="J38" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K38" t="n">
         <v>-31000000</v>
       </c>
       <c r="L38" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="M38" t="n">
         <v>0.03929424848359133</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="P38" t="n">
-        <v>-52034.700359843</v>
+        <v>-11250.80366190433</v>
       </c>
       <c r="Q38" t="n">
-        <v>-52034.700359843</v>
+        <v>-11250.80366190433</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J39" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M39" t="n">
         <v>0.03936107056455495</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="P39" t="n">
-        <v>-3136.119171026371</v>
+        <v>-3159.178560060345</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3136.119171026371</v>
+        <v>-3159.178560060345</v>
       </c>
     </row>
     <row r="40">
@@ -3804,19 +3804,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J40" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K40" t="n">
         <v>-62000000</v>
       </c>
       <c r="L40" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="M40" t="n">
         <v>0.03942868733737526</v>
@@ -3828,10 +3828,10 @@
         <v>0.0001712813743293129</v>
       </c>
       <c r="P40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K41" t="n">
         <v>-620000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="M41" t="n">
         <v>0.03432749872940843</v>
@@ -3889,10 +3889,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="P41" t="n">
-        <v>-37502402.5896528</v>
+        <v>-36247659.17335165</v>
       </c>
       <c r="Q41" t="n">
-        <v>-37502402.5896528</v>
+        <v>-36247659.17335165</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J42" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K42" t="n">
         <v>-62000000</v>
       </c>
       <c r="L42" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="M42" t="n">
         <v>0.03782665436246635</v>
@@ -3950,10 +3950,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="P42" t="n">
-        <v>20225851.18886004</v>
+        <v>17642871.74051509</v>
       </c>
       <c r="Q42" t="n">
-        <v>10112925.59443002</v>
+        <v>8821435.870257543</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J43" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M43" t="n">
         <v>0.03830470017405307</v>
@@ -4011,10 +4011,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="P43" t="n">
-        <v>15125300.47283325</v>
+        <v>14740223.1984997</v>
       </c>
       <c r="Q43" t="n">
-        <v>7562650.236416627</v>
+        <v>7370111.599249849</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I44" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J44" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K44" t="n">
         <v>-124000000</v>
       </c>
       <c r="L44" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="M44" t="n">
         <v>0.03852218097221538</v>
@@ -4072,10 +4072,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="P44" t="n">
-        <v>12817964.2476002</v>
+        <v>12603538.27983324</v>
       </c>
       <c r="Q44" t="n">
-        <v>6408982.1238001</v>
+        <v>6301769.139916618</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I45" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J45" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K45" t="n">
         <v>-62000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="M45" t="n">
         <v>0.03873510939427094</v>
@@ -4133,10 +4133,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="P45" t="n">
-        <v>-3807446.827050986</v>
+        <v>-3902076.660081655</v>
       </c>
       <c r="Q45" t="n">
-        <v>-3807446.827050986</v>
+        <v>-3902076.660081655</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I46" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J46" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K46" t="n">
         <v>-62000000</v>
       </c>
       <c r="L46" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="M46" t="n">
         <v>0.03888939094511485</v>
@@ -4194,10 +4194,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="P46" t="n">
-        <v>-2880089.781921424</v>
+        <v>-2978372.895632596</v>
       </c>
       <c r="Q46" t="n">
-        <v>-2880089.781921424</v>
+        <v>-2978372.895632596</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J47" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K47" t="n">
         <v>-31000000</v>
       </c>
       <c r="L47" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="M47" t="n">
         <v>0.03901400018340251</v>
@@ -4255,10 +4255,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="P47" t="n">
-        <v>380326.3001034642</v>
+        <v>1972311.876162619</v>
       </c>
       <c r="Q47" t="n">
-        <v>190163.1500517321</v>
+        <v>986155.9380813093</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I48" t="n">
         <v>2250000</v>
       </c>
       <c r="J48" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K48" t="n">
         <v>-31000000</v>
       </c>
       <c r="L48" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="M48" t="n">
         <v>0.03908855826627113</v>
@@ -4316,10 +4316,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="P48" t="n">
-        <v>539594.5311432841</v>
+        <v>-841367.9283942515</v>
       </c>
       <c r="Q48" t="n">
-        <v>269797.265571642</v>
+        <v>-841367.9283942515</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I49" t="n">
         <v>2250000</v>
       </c>
       <c r="J49" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K49" t="n">
         <v>-31000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="M49" t="n">
         <v>0.03915884386251234</v>
@@ -4377,10 +4377,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="P49" t="n">
-        <v>-57310.46479594545</v>
+        <v>-52992.93061580981</v>
       </c>
       <c r="Q49" t="n">
-        <v>-57310.46479594545</v>
+        <v>-52992.93061580981</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I50" t="n">
         <v>2250000</v>
       </c>
       <c r="J50" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K50" t="n">
         <v>-31000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="M50" t="n">
         <v>0.03922681220647117</v>
@@ -4438,10 +4438,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="P50" t="n">
-        <v>-31548.28330481974</v>
+        <v>-25810.93439611698</v>
       </c>
       <c r="Q50" t="n">
-        <v>-31548.28330481974</v>
+        <v>-25810.93439611698</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I51" t="n">
         <v>2250000</v>
       </c>
       <c r="J51" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K51" t="n">
         <v>-31000000</v>
       </c>
       <c r="L51" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="M51" t="n">
         <v>0.03929424848359133</v>
@@ -4499,10 +4499,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="P51" t="n">
-        <v>103497.0722993473</v>
+        <v>-1967.060839978806</v>
       </c>
       <c r="Q51" t="n">
-        <v>51748.53614967367</v>
+        <v>-1967.060839978806</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J52" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M52" t="n">
         <v>0.03936107056455495</v>
@@ -4560,10 +4560,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="P52" t="n">
-        <v>14053.41532337252</v>
+        <v>14156.74786704356</v>
       </c>
       <c r="Q52" t="n">
-        <v>7026.70766168626</v>
+        <v>7078.373933521779</v>
       </c>
     </row>
     <row r="53">
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J53" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K53" t="n">
         <v>-62000000</v>
       </c>
       <c r="L53" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="M53" t="n">
         <v>0.03942868733737526</v>
@@ -4621,10 +4621,10 @@
         <v>0.003319954993421748</v>
       </c>
       <c r="P53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K54" t="n">
         <v>-620000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="M54" t="n">
         <v>0.03432749872940843</v>
@@ -4682,10 +4682,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="P54" t="n">
-        <v>-46934947.46025104</v>
+        <v>-45364612.96823002</v>
       </c>
       <c r="Q54" t="n">
-        <v>-46934947.46025104</v>
+        <v>-45364612.96823002</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J55" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K55" t="n">
         <v>-62000000</v>
       </c>
       <c r="L55" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="M55" t="n">
         <v>0.03782665436246635</v>
@@ -4743,10 +4743,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="P55" t="n">
-        <v>26218365.33344426</v>
+        <v>22870100.86768048</v>
       </c>
       <c r="Q55" t="n">
-        <v>13109182.66672213</v>
+        <v>11435050.43384024</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J56" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M56" t="n">
         <v>0.03830470017405307</v>
@@ -4804,10 +4804,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="P56" t="n">
-        <v>20421006.38046642</v>
+        <v>19901104.94179668</v>
       </c>
       <c r="Q56" t="n">
-        <v>10210503.19023321</v>
+        <v>9950552.470898338</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I57" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J57" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K57" t="n">
         <v>-124000000</v>
       </c>
       <c r="L57" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="M57" t="n">
         <v>0.03852218097221538</v>
@@ -4865,10 +4865,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="P57" t="n">
-        <v>18110090.90314015</v>
+        <v>17807135.32507474</v>
       </c>
       <c r="Q57" t="n">
-        <v>9055045.451570075</v>
+        <v>8903567.662537372</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I58" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J58" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K58" t="n">
         <v>-62000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="M58" t="n">
         <v>0.03873510939427094</v>
@@ -4926,10 +4926,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="P58" t="n">
-        <v>-5667074.721781447</v>
+        <v>-5807923.526519679</v>
       </c>
       <c r="Q58" t="n">
-        <v>-5667074.721781447</v>
+        <v>-5807923.526519679</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I59" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J59" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K59" t="n">
         <v>-62000000</v>
       </c>
       <c r="L59" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="M59" t="n">
         <v>0.03888939094511485</v>
@@ -4987,10 +4987,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="P59" t="n">
-        <v>-4553029.167480368</v>
+        <v>-4708401.366710636</v>
       </c>
       <c r="Q59" t="n">
-        <v>-4553029.167480368</v>
+        <v>-4708401.366710636</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J60" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K60" t="n">
         <v>-31000000</v>
       </c>
       <c r="L60" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="M60" t="n">
         <v>0.03901400018340251</v>
@@ -5048,10 +5048,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="P60" t="n">
-        <v>644476.2028909577</v>
+        <v>3342151.380328503</v>
       </c>
       <c r="Q60" t="n">
-        <v>322238.1014454789</v>
+        <v>1671075.690164251</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I61" t="n">
         <v>2250000</v>
       </c>
       <c r="J61" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K61" t="n">
         <v>-31000000</v>
       </c>
       <c r="L61" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="M61" t="n">
         <v>0.03908855826627113</v>
@@ -5109,10 +5109,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="P61" t="n">
-        <v>992719.2329672207</v>
+        <v>-1547906.949221786</v>
       </c>
       <c r="Q61" t="n">
-        <v>496359.6164836104</v>
+        <v>-1547906.949221786</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I62" t="n">
         <v>2250000</v>
       </c>
       <c r="J62" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K62" t="n">
         <v>-31000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="M62" t="n">
         <v>0.03915884386251234</v>
@@ -5170,10 +5170,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="P62" t="n">
-        <v>-116057.7847400222</v>
+        <v>-107314.4696357043</v>
       </c>
       <c r="Q62" t="n">
-        <v>-116057.7847400222</v>
+        <v>-107314.4696357043</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I63" t="n">
         <v>2250000</v>
       </c>
       <c r="J63" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K63" t="n">
         <v>-31000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="M63" t="n">
         <v>0.03922681220647117</v>
@@ -5231,10 +5231,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="P63" t="n">
-        <v>-71810.11365768088</v>
+        <v>-58750.7762209344</v>
       </c>
       <c r="Q63" t="n">
-        <v>-71810.11365768088</v>
+        <v>-58750.7762209344</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I64" t="n">
         <v>2250000</v>
       </c>
       <c r="J64" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K64" t="n">
         <v>-31000000</v>
       </c>
       <c r="L64" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="M64" t="n">
         <v>0.03929424848359133</v>
@@ -5292,10 +5292,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="P64" t="n">
-        <v>272149.4614739451</v>
+        <v>-5172.460789406253</v>
       </c>
       <c r="Q64" t="n">
-        <v>136074.7307369725</v>
+        <v>-5172.460789406253</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J65" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M65" t="n">
         <v>0.03936107056455495</v>
@@ -5353,10 +5353,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="P65" t="n">
-        <v>44452.29201593011</v>
+        <v>44779.14269957671</v>
       </c>
       <c r="Q65" t="n">
-        <v>22226.14600796506</v>
+        <v>22389.57134978836</v>
       </c>
     </row>
     <row r="66">
@@ -5390,19 +5390,19 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J66" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K66" t="n">
         <v>-62000000</v>
       </c>
       <c r="L66" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="M66" t="n">
         <v>0.03942868733737526</v>
@@ -5414,10 +5414,10 @@
         <v>0.01346967956071188</v>
       </c>
       <c r="P66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K67" t="n">
         <v>-620000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="M67" t="n">
         <v>0.03432749872940843</v>
@@ -5475,10 +5475,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="P67" t="n">
-        <v>24926411.20961912</v>
+        <v>23382381.53250516</v>
       </c>
       <c r="Q67" t="n">
-        <v>12463205.60480956</v>
+        <v>11691190.76625258</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J68" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K68" t="n">
         <v>-62000000</v>
       </c>
       <c r="L68" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="M68" t="n">
         <v>0.03782665436246635</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="P68" t="n">
-        <v>-27978030.63722467</v>
+        <v>-24638913.08788164</v>
       </c>
       <c r="Q68" t="n">
-        <v>-27978030.63722467</v>
+        <v>-24638913.08788164</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J69" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M69" t="n">
         <v>0.03830470017405307</v>
@@ -5597,10 +5597,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="P69" t="n">
-        <v>-20318974.41986052</v>
+        <v>-19801670.62805112</v>
       </c>
       <c r="Q69" t="n">
-        <v>-20318974.41986052</v>
+        <v>-19801670.62805112</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I70" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J70" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K70" t="n">
         <v>-124000000</v>
       </c>
       <c r="L70" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="M70" t="n">
         <v>0.03852218097221538</v>
@@ -5658,10 +5658,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="P70" t="n">
-        <v>-20535840.25681047</v>
+        <v>-20234950.91453646</v>
       </c>
       <c r="Q70" t="n">
-        <v>-20535840.25681047</v>
+        <v>-20234950.91453646</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I71" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J71" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K71" t="n">
         <v>-62000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="M71" t="n">
         <v>0.03873510939427094</v>
@@ -5719,10 +5719,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="P71" t="n">
-        <v>4574413.650521738</v>
+        <v>4714088.637765296</v>
       </c>
       <c r="Q71" t="n">
-        <v>2287206.825260869</v>
+        <v>2357044.318882648</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I72" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J72" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K72" t="n">
         <v>-62000000</v>
       </c>
       <c r="L72" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="M72" t="n">
         <v>0.03888939094511485</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="P72" t="n">
-        <v>3665721.943105661</v>
+        <v>3819603.605249374</v>
       </c>
       <c r="Q72" t="n">
-        <v>1832860.971552831</v>
+        <v>1909801.802624687</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J73" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K73" t="n">
         <v>-31000000</v>
       </c>
       <c r="L73" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="M73" t="n">
         <v>0.03901400018340251</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="P73" t="n">
-        <v>-971307.2882109547</v>
+        <v>-3640472.141650804</v>
       </c>
       <c r="Q73" t="n">
-        <v>-971307.2882109547</v>
+        <v>-3640472.141650804</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I74" t="n">
         <v>2250000</v>
       </c>
       <c r="J74" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K74" t="n">
         <v>-31000000</v>
       </c>
       <c r="L74" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="M74" t="n">
         <v>0.03908855826627113</v>
@@ -5902,10 +5902,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="P74" t="n">
-        <v>-1237738.428532413</v>
+        <v>1273911.216587889</v>
       </c>
       <c r="Q74" t="n">
-        <v>-1237738.428532413</v>
+        <v>636955.6082939446</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I75" t="n">
         <v>2250000</v>
       </c>
       <c r="J75" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K75" t="n">
         <v>-31000000</v>
       </c>
       <c r="L75" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="M75" t="n">
         <v>0.03915884386251234</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="P75" t="n">
-        <v>-74700.70660590389</v>
+        <v>-83339.80282946698</v>
       </c>
       <c r="Q75" t="n">
-        <v>-74700.70660590389</v>
+        <v>-83339.80282946698</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I76" t="n">
         <v>2250000</v>
       </c>
       <c r="J76" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K76" t="n">
         <v>-31000000</v>
       </c>
       <c r="L76" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="M76" t="n">
         <v>0.03922681220647117</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="P76" t="n">
-        <v>-60137.58028323063</v>
+        <v>-73035.67850163192</v>
       </c>
       <c r="Q76" t="n">
-        <v>-60137.58028323063</v>
+        <v>-73035.67850163192</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I77" t="n">
         <v>2250000</v>
       </c>
       <c r="J77" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K77" t="n">
         <v>-31000000</v>
       </c>
       <c r="L77" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="M77" t="n">
         <v>0.03929424848359133</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="P77" t="n">
-        <v>-349365.0873889751</v>
+        <v>-75538.78426041281</v>
       </c>
       <c r="Q77" t="n">
-        <v>-349365.0873889751</v>
+        <v>-75538.78426041281</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J78" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M78" t="n">
         <v>0.03936107056455495</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="P78" t="n">
-        <v>-43885.49532128132</v>
+        <v>-44208.17843833612</v>
       </c>
       <c r="Q78" t="n">
-        <v>-43885.49532128132</v>
+        <v>-44208.17843833612</v>
       </c>
     </row>
     <row r="79">
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J79" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K79" t="n">
         <v>-62000000</v>
       </c>
       <c r="L79" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="M79" t="n">
         <v>0.03942868733737526</v>
@@ -6207,10 +6207,10 @@
         <v>-0.01329726695768341</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="80">
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="K80" t="n">
         <v>-620000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="M80" t="n">
         <v>0.03432749872940843</v>
@@ -6268,10 +6268,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="P80" t="n">
-        <v>7263233.497380241</v>
+        <v>6813323.240446202</v>
       </c>
       <c r="Q80" t="n">
-        <v>3631616.74869012</v>
+        <v>3406661.620223101</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="I81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J81" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="K81" t="n">
         <v>-62000000</v>
       </c>
       <c r="L81" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="M81" t="n">
         <v>0.03782665436246635</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="P81" t="n">
-        <v>-8705844.011418846</v>
+        <v>-7666820.325395201</v>
       </c>
       <c r="Q81" t="n">
-        <v>-8705844.011418846</v>
+        <v>-7666820.325395201</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="I82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J82" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="M82" t="n">
         <v>0.03830470017405307</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="P82" t="n">
-        <v>-6879235.741925485</v>
+        <v>-6704096.256018637</v>
       </c>
       <c r="Q82" t="n">
-        <v>-6879235.741925485</v>
+        <v>-6704096.256018637</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="I83" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J83" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="K83" t="n">
         <v>-124000000</v>
       </c>
       <c r="L83" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="M83" t="n">
         <v>0.03852218097221538</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="P83" t="n">
-        <v>-7554052.448134966</v>
+        <v>-7443371.129805716</v>
       </c>
       <c r="Q83" t="n">
-        <v>-7554052.448134966</v>
+        <v>-7443371.129805716</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="I84" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J84" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="K84" t="n">
         <v>-62000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="M84" t="n">
         <v>0.03873510939427094</v>
@@ -6512,10 +6512,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="P84" t="n">
-        <v>1828866.162195075</v>
+        <v>1884708.697958241</v>
       </c>
       <c r="Q84" t="n">
-        <v>914433.0810975374</v>
+        <v>942354.3489791203</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="I85" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J85" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="K85" t="n">
         <v>-62000000</v>
       </c>
       <c r="L85" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="M85" t="n">
         <v>0.03888939094511485</v>
@@ -6573,10 +6573,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="P85" t="n">
-        <v>1593599.413870349</v>
+        <v>1660496.393620498</v>
       </c>
       <c r="Q85" t="n">
-        <v>796799.7069351746</v>
+        <v>830248.196810249</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="I86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J86" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="K86" t="n">
         <v>-31000000</v>
       </c>
       <c r="L86" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="M86" t="n">
         <v>0.03901400018340251</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="P86" t="n">
-        <v>-458888.00901441</v>
+        <v>-1719918.128105035</v>
       </c>
       <c r="Q86" t="n">
-        <v>-458888.00901441</v>
+        <v>-1719918.128105035</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="I87" t="n">
         <v>2250000</v>
       </c>
       <c r="J87" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="K87" t="n">
         <v>-31000000</v>
       </c>
       <c r="L87" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="M87" t="n">
         <v>0.03908855826627113</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="P87" t="n">
-        <v>-635987.7169835642</v>
+        <v>654574.397627883</v>
       </c>
       <c r="Q87" t="n">
-        <v>-635987.7169835642</v>
+        <v>327287.1988139415</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="I88" t="n">
         <v>2250000</v>
       </c>
       <c r="J88" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="K88" t="n">
         <v>-31000000</v>
       </c>
       <c r="L88" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="M88" t="n">
         <v>0.03915884386251234</v>
@@ -6756,10 +6756,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="P88" t="n">
-        <v>-41685.28966741191</v>
+        <v>-46506.17081976515</v>
       </c>
       <c r="Q88" t="n">
-        <v>-41685.28966741191</v>
+        <v>-46506.17081976515</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="I89" t="n">
         <v>2250000</v>
       </c>
       <c r="J89" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="K89" t="n">
         <v>-31000000</v>
       </c>
       <c r="L89" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="M89" t="n">
         <v>0.03922681220647117</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="P89" t="n">
-        <v>-36469.49657984389</v>
+        <v>-44291.34685461532</v>
       </c>
       <c r="Q89" t="n">
-        <v>-36469.49657984389</v>
+        <v>-44291.34685461532</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="I90" t="n">
         <v>2250000</v>
       </c>
       <c r="J90" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="K90" t="n">
         <v>-31000000</v>
       </c>
       <c r="L90" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="M90" t="n">
         <v>0.03929424848359133</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="P90" t="n">
-        <v>-230190.9807597766</v>
+        <v>-49771.27784650621</v>
       </c>
       <c r="Q90" t="n">
-        <v>-230190.9807597766</v>
+        <v>-49771.27784650621</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="I91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J91" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="M91" t="n">
         <v>0.03936107056455495</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="P91" t="n">
-        <v>-31416.7430700596</v>
+        <v>-31647.74542077571</v>
       </c>
       <c r="Q91" t="n">
-        <v>-31416.7430700596</v>
+        <v>-31647.74542077571</v>
       </c>
     </row>
     <row r="92">
@@ -6976,19 +6976,19 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="I92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J92" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="K92" t="n">
         <v>-62000000</v>
       </c>
       <c r="L92" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="M92" t="n">
         <v>0.03942868733737526</v>
@@ -7000,10 +7000,10 @@
         <v>-0.01034243719640493</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38693708.36000007</v>
+        <v>33204891.25999999</v>
       </c>
       <c r="D2" t="n">
-        <v>19346854.18000004</v>
+        <v>16602445.63</v>
       </c>
       <c r="E2" t="n">
-        <v>3.224475696666672</v>
+        <v>2.767074271666666</v>
       </c>
       <c r="F2" t="n">
-        <v>1.612237848333336</v>
+        <v>1.383537135833333</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-42208098.56999999</v>
+        <v>-36949558.86999995</v>
       </c>
       <c r="D3" t="n">
-        <v>-42208098.56999999</v>
+        <v>-36949558.86999995</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.5173415475</v>
+        <v>-3.079129905833329</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.5173415475</v>
+        <v>-3.079129905833329</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23719590.56</v>
+        <v>24037176.79000008</v>
       </c>
       <c r="D4" t="n">
-        <v>11859795.28</v>
+        <v>12018588.39500004</v>
       </c>
       <c r="E4" t="n">
-        <v>1.976632546666667</v>
+        <v>2.00309806583334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9883162733333334</v>
+        <v>1.00154903291667</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-23887034.91999996</v>
+        <v>-25108557.89999998</v>
       </c>
       <c r="D5" t="n">
-        <v>-23887034.91999996</v>
+        <v>-25108557.89999998</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.99058624333333</v>
+        <v>-2.092379824999998</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.99058624333333</v>
+        <v>-2.092379824999998</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5286286.149999976</v>
+        <v>-8558612.109999955</v>
       </c>
       <c r="D6" t="n">
-        <v>-5286286.149999976</v>
+        <v>-8558612.109999955</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4405238458333314</v>
+        <v>-0.7132176758333296</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4405238458333314</v>
+        <v>-0.7132176758333296</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1547548.280000031</v>
+        <v>4684805.470000029</v>
       </c>
       <c r="D7" t="n">
-        <v>773774.1400000155</v>
+        <v>2342402.735000014</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1289623566666692</v>
+        <v>0.3904004558333357</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06448117833333462</v>
+        <v>0.1952002279166679</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-17917160.22999996</v>
+        <v>-15844724.27999997</v>
       </c>
       <c r="D8" t="n">
-        <v>-17917160.22999996</v>
+        <v>-15844724.27999997</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.49309668583333</v>
+        <v>-1.320393689999998</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.49309668583333</v>
+        <v>-1.320393689999998</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="F2" t="n">
         <v>-620000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J2" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="K2" t="n">
-        <v>-12995348.6958937</v>
+        <v>-13050005.93185206</v>
       </c>
       <c r="L2" t="n">
-        <v>6812334.997263561</v>
+        <v>6866992.233221918</v>
       </c>
       <c r="M2" t="n">
-        <v>-12995348.6958937</v>
+        <v>-13050005.93185206</v>
       </c>
       <c r="N2" t="n">
-        <v>6812334.997263561</v>
+        <v>6866992.233221918</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="F3" t="n">
         <v>-62000000</v>
       </c>
       <c r="G3" t="n">
-        <v>923715944.4299999</v>
+        <v>921293400.75</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J3" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="K3" t="n">
-        <v>7899062.823941666</v>
+        <v>7876856.173541667</v>
       </c>
       <c r="L3" t="n">
-        <v>-8467396.157274999</v>
+        <v>-8445189.506874999</v>
       </c>
       <c r="M3" t="n">
-        <v>7078253.723485045</v>
+        <v>7056047.073085045</v>
       </c>
       <c r="N3" t="n">
-        <v>-7646587.056818378</v>
+        <v>-7624380.406418378</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J4" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K4" t="n">
-        <v>7092348.343916668</v>
+        <v>6849605.095833334</v>
       </c>
       <c r="L4" t="n">
-        <v>-7092348.343916668</v>
+        <v>-6849605.095833334</v>
       </c>
       <c r="M4" t="n">
-        <v>6667892.065377855</v>
+        <v>6425148.817294521</v>
       </c>
       <c r="N4" t="n">
-        <v>-6667892.065377855</v>
+        <v>-6425148.817294521</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="F5" t="n">
         <v>-124000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1114570715.1</v>
+        <v>1372487704.21</v>
       </c>
       <c r="H5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J5" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="K5" t="n">
-        <v>7429280.363250002</v>
+        <v>9363657.781574998</v>
       </c>
       <c r="L5" t="n">
-        <v>-8359280.363250002</v>
+        <v>-10293657.781575</v>
       </c>
       <c r="M5" t="n">
-        <v>6451933.705715755</v>
+        <v>8386311.124040753</v>
       </c>
       <c r="N5" t="n">
-        <v>-7381933.705715755</v>
+        <v>-9316311.124040753</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="F6" t="n">
         <v>-62000000</v>
       </c>
       <c r="G6" t="n">
-        <v>-189621108.9</v>
+        <v>-182620576.92</v>
       </c>
       <c r="H6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J6" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="K6" t="n">
-        <v>-1677474.059333334</v>
+        <v>-1630803.846133334</v>
       </c>
       <c r="L6" t="n">
-        <v>1264140.726</v>
+        <v>1217470.5128</v>
       </c>
       <c r="M6" t="n">
-        <v>-2277145.949744293</v>
+        <v>-2230475.736544293</v>
       </c>
       <c r="N6" t="n">
-        <v>1863812.616410959</v>
+        <v>1817142.403210959</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="F7" t="n">
         <v>-62000000</v>
       </c>
       <c r="G7" t="n">
-        <v>-190737100.49</v>
+        <v>-189489410.97</v>
       </c>
       <c r="H7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J7" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="K7" t="n">
-        <v>-1474299.752858333</v>
+        <v>-1467021.563991667</v>
       </c>
       <c r="L7" t="n">
-        <v>1112633.086191666</v>
+        <v>1105354.897325</v>
       </c>
       <c r="M7" t="n">
-        <v>-1999144.889844634</v>
+        <v>-1991866.700977968</v>
       </c>
       <c r="N7" t="n">
-        <v>1637478.223177968</v>
+        <v>1630200.034311301</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="F8" t="n">
         <v>-31000000</v>
       </c>
       <c r="G8" t="n">
-        <v>428219075.5699999</v>
+        <v>173015112.97</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J8" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="K8" t="n">
-        <v>1986095.37785</v>
+        <v>710075.5648500002</v>
       </c>
       <c r="L8" t="n">
-        <v>-2141095.37785</v>
+        <v>-865075.5648500002</v>
       </c>
       <c r="M8" t="n">
-        <v>1536252.336754109</v>
+        <v>260232.5237541097</v>
       </c>
       <c r="N8" t="n">
-        <v>-1691252.336754109</v>
+        <v>-415232.5237541097</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="F9" t="n">
         <v>-31000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-156307218.49</v>
+        <v>-20277242.50999999</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-780446.7437083333</v>
+        <v>-213655.177125</v>
       </c>
       <c r="L9" t="n">
-        <v>651280.0770416667</v>
+        <v>84488.51045833329</v>
       </c>
       <c r="M9" t="n">
-        <v>-771071.7437083333</v>
+        <v>-204280.177125</v>
       </c>
       <c r="N9" t="n">
-        <v>641905.0770416667</v>
+        <v>75113.51045833329</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="F10" t="n">
         <v>-31000000</v>
       </c>
       <c r="G10" t="n">
-        <v>11392415.84999999</v>
+        <v>10746230.59999999</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J10" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-65358.61383333337</v>
+        <v>-67512.5646666667</v>
       </c>
       <c r="L10" t="n">
-        <v>-37974.71949999998</v>
+        <v>-35820.76866666665</v>
       </c>
       <c r="M10" t="n">
-        <v>-57858.61383333337</v>
+        <v>-60012.5646666667</v>
       </c>
       <c r="N10" t="n">
-        <v>-45474.71949999998</v>
+        <v>-43320.76866666665</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="F11" t="n">
         <v>-31000000</v>
       </c>
       <c r="G11" t="n">
-        <v>15025197.6</v>
+        <v>9731487.229999997</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J11" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="K11" t="n">
-        <v>-39937.00599999999</v>
+        <v>-53171.28192500001</v>
       </c>
       <c r="L11" t="n">
-        <v>-37562.99400000001</v>
+        <v>-24328.71807499999</v>
       </c>
       <c r="M11" t="n">
-        <v>-34312.00599999999</v>
+        <v>-47546.28192500001</v>
       </c>
       <c r="N11" t="n">
-        <v>-43187.99400000001</v>
+        <v>-29953.71807499999</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="F12" t="n">
         <v>-31000000</v>
       </c>
       <c r="G12" t="n">
-        <v>26786789.9</v>
+        <v>11909921.49</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J12" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="K12" t="n">
-        <v>-7022.016833333335</v>
+        <v>-31816.79751666665</v>
       </c>
       <c r="L12" t="n">
-        <v>-44644.64983333332</v>
+        <v>-19849.86915</v>
       </c>
       <c r="M12" t="n">
-        <v>-3272.016833333335</v>
+        <v>-28066.79751666666</v>
       </c>
       <c r="N12" t="n">
-        <v>-48394.64983333332</v>
+        <v>-23599.86915</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J13" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K13" t="n">
-        <v>28800.66368333335</v>
+        <v>29741.23346666668</v>
       </c>
       <c r="L13" t="n">
-        <v>-28800.66368333335</v>
+        <v>-29741.23346666668</v>
       </c>
       <c r="M13" t="n">
-        <v>30685.93765593609</v>
+        <v>31626.50743926942</v>
       </c>
       <c r="N13" t="n">
-        <v>-30685.93765593609</v>
+        <v>-31626.50743926942</v>
       </c>
     </row>
     <row r="14">
@@ -1087,34 +1087,34 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="F14" t="n">
         <v>-62000000</v>
       </c>
       <c r="G14" t="n">
-        <v>129606409.5</v>
+        <v>-17556538.55</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J14" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="K14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7395700.684181305</v>
+        <v>8315948.686056274</v>
       </c>
       <c r="C2" t="n">
-        <v>-16368714.38281144</v>
+        <v>-17288962.38468641</v>
       </c>
       <c r="D2" t="n">
-        <v>3626863.853131076</v>
+        <v>4547111.855006047</v>
       </c>
       <c r="E2" t="n">
-        <v>-12599877.55176121</v>
+        <v>-13520125.55363619</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-45010257.53</v>
+        <v>-44992749.09</v>
       </c>
       <c r="D2" t="n">
-        <v>-70107770.4116428</v>
+        <v>-70505634.63268048</v>
       </c>
       <c r="E2" t="n">
-        <v>-115118027.9416428</v>
+        <v>-115498383.7226805</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74990879.70999999</v>
+        <v>60616755.16</v>
       </c>
       <c r="D3" t="n">
-        <v>7822827.81230137</v>
+        <v>7656881.216315068</v>
       </c>
       <c r="E3" t="n">
-        <v>82813707.52230138</v>
+        <v>68273636.37631507</v>
       </c>
     </row>
     <row r="4">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>518396088.04</v>
+        <v>459987425.03</v>
       </c>
       <c r="D5" t="n">
-        <v>47983973.33008273</v>
+        <v>46495852.15232349</v>
       </c>
       <c r="E5" t="n">
-        <v>566380061.3700827</v>
+        <v>506483277.1823235</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>551701010.92</v>
+        <v>478935731.8</v>
       </c>
       <c r="C2" t="n">
-        <v>-14300969.26925871</v>
+        <v>-16352901.26404192</v>
       </c>
       <c r="D2" t="n">
-        <v>537400041.6507413</v>
+        <v>462582830.5359581</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K2" t="n">
         <v>-620000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="M2" t="n">
         <v>0.03432749872940843</v>
@@ -1510,10 +1510,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="P2" t="n">
-        <v>-32494633.94614996</v>
+        <v>-32631303.37430746</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32494633.94614996</v>
+        <v>-32631303.37430746</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J3" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K3" t="n">
         <v>-62000000</v>
       </c>
       <c r="L3" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="M3" t="n">
         <v>0.03782665436246635</v>
@@ -1571,10 +1571,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="P3" t="n">
-        <v>17770533.45230579</v>
+        <v>17714781.8447465</v>
       </c>
       <c r="Q3" t="n">
-        <v>8885266.726152895</v>
+        <v>8857390.922373248</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J4" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M4" t="n">
         <v>0.03830470017405307</v>
@@ -1632,10 +1632,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="P4" t="n">
-        <v>16811911.25825904</v>
+        <v>16199877.06434811</v>
       </c>
       <c r="Q4" t="n">
-        <v>8405955.629129518</v>
+        <v>8099938.532174057</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J5" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K5" t="n">
         <v>-124000000</v>
       </c>
       <c r="L5" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="M5" t="n">
         <v>0.03852218097221538</v>
@@ -1693,10 +1693,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="P5" t="n">
-        <v>16336466.04784997</v>
+        <v>21234360.61087049</v>
       </c>
       <c r="Q5" t="n">
-        <v>8168233.023924986</v>
+        <v>10617180.30543524</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J6" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K6" t="n">
         <v>-62000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="M6" t="n">
         <v>0.03873510939427094</v>
@@ -1754,10 +1754,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="P6" t="n">
-        <v>-5790491.76086683</v>
+        <v>-5671815.360242249</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5790491.76086683</v>
+        <v>-5671815.360242249</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J7" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K7" t="n">
         <v>-62000000</v>
       </c>
       <c r="L7" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="M7" t="n">
         <v>0.03888939094511485</v>
@@ -1815,10 +1815,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="P7" t="n">
-        <v>-5105458.722928206</v>
+        <v>-5086871.529461038</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5105458.722928206</v>
+        <v>-5086871.529461038</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J8" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K8" t="n">
         <v>-31000000</v>
       </c>
       <c r="L8" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="M8" t="n">
         <v>0.03901400018340251</v>
@@ -1876,10 +1876,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="P8" t="n">
-        <v>3940141.833224572</v>
+        <v>667437.9128207581</v>
       </c>
       <c r="Q8" t="n">
-        <v>1970070.916612286</v>
+        <v>333718.956410379</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I9" t="n">
         <v>2250000</v>
       </c>
       <c r="J9" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K9" t="n">
         <v>-31000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="M9" t="n">
         <v>0.03908855826627113</v>
@@ -1937,10 +1937,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="P9" t="n">
-        <v>-1986148.711206025</v>
+        <v>-526190.7388415849</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1986148.711206025</v>
+        <v>-526190.7388415849</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I10" t="n">
         <v>2250000</v>
       </c>
       <c r="J10" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K10" t="n">
         <v>-31000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="M10" t="n">
         <v>0.03915884386251234</v>
@@ -1998,10 +1998,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="P10" t="n">
-        <v>-149667.0570893367</v>
+        <v>-155238.837347826</v>
       </c>
       <c r="Q10" t="n">
-        <v>-149667.0570893367</v>
+        <v>-155238.837347826</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I11" t="n">
         <v>2250000</v>
       </c>
       <c r="J11" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K11" t="n">
         <v>-31000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="M11" t="n">
         <v>0.03922681220647117</v>
@@ -2059,10 +2059,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="P11" t="n">
-        <v>-89137.46036406193</v>
+        <v>-123518.1300839188</v>
       </c>
       <c r="Q11" t="n">
-        <v>-89137.46036406193</v>
+        <v>-123518.1300839188</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I12" t="n">
         <v>2250000</v>
       </c>
       <c r="J12" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K12" t="n">
         <v>-31000000</v>
       </c>
       <c r="L12" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="M12" t="n">
         <v>0.03929424848359133</v>
@@ -2120,10 +2120,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="P12" t="n">
-        <v>-8536.538861164656</v>
+        <v>-73224.96182435016</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8536.538861164656</v>
+        <v>-73224.96182435016</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J13" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M13" t="n">
         <v>0.03936107056455495</v>
@@ -2181,10 +2181,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="P13" t="n">
-        <v>80400.62277743395</v>
+        <v>82865.02185148366</v>
       </c>
       <c r="Q13" t="n">
-        <v>40200.31138871697</v>
+        <v>41432.51092574183</v>
       </c>
     </row>
     <row r="14">
@@ -2218,19 +2218,19 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J14" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K14" t="n">
         <v>-62000000</v>
       </c>
       <c r="L14" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="M14" t="n">
         <v>0.03942868733737526</v>
@@ -2242,10 +2242,10 @@
         <v>0.02631330603469872</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K15" t="n">
         <v>-620000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="M15" t="n">
         <v>0.03432749872940843</v>
@@ -2303,10 +2303,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="P15" t="n">
-        <v>17030836.66542407</v>
+        <v>17167479.74867882</v>
       </c>
       <c r="Q15" t="n">
-        <v>8515418.332712036</v>
+        <v>8583739.874339411</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J16" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K16" t="n">
         <v>-62000000</v>
       </c>
       <c r="L16" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="M16" t="n">
         <v>0.03782665436246635</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="P16" t="n">
-        <v>-19156040.63783142</v>
+        <v>-19100409.08687521</v>
       </c>
       <c r="Q16" t="n">
-        <v>-19156040.63783142</v>
+        <v>-19100409.08687521</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J17" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M17" t="n">
         <v>0.03830470017405307</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="P17" t="n">
-        <v>-16740457.22797247</v>
+        <v>-16131024.30343279</v>
       </c>
       <c r="Q17" t="n">
-        <v>-16740457.22797247</v>
+        <v>-16131024.30343279</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I18" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J18" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K18" t="n">
         <v>-124000000</v>
       </c>
       <c r="L18" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="M18" t="n">
         <v>0.03852218097221538</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="P18" t="n">
-        <v>-18574127.0487122</v>
+        <v>-23441330.32639927</v>
       </c>
       <c r="Q18" t="n">
-        <v>-18574127.0487122</v>
+        <v>-23441330.32639927</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I19" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J19" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K19" t="n">
         <v>-62000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="M19" t="n">
         <v>0.03873510939427094</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="P19" t="n">
-        <v>4700056.675846255</v>
+        <v>4582366.385962811</v>
       </c>
       <c r="Q19" t="n">
-        <v>2350028.337923128</v>
+        <v>2291183.192981406</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I20" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J20" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K20" t="n">
         <v>-62000000</v>
       </c>
       <c r="L20" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="M20" t="n">
         <v>0.03888939094511485</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="P20" t="n">
-        <v>4138380.973767051</v>
+        <v>4119986.885892807</v>
       </c>
       <c r="Q20" t="n">
-        <v>2069190.486883525</v>
+        <v>2059993.442946403</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J21" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K21" t="n">
         <v>-31000000</v>
       </c>
       <c r="L21" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="M21" t="n">
         <v>0.03901400018340251</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="P21" t="n">
-        <v>-4283757.348108819</v>
+        <v>-1051738.605854207</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4283757.348108819</v>
+        <v>-1051738.605854207</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I22" t="n">
         <v>2250000</v>
       </c>
       <c r="J22" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K22" t="n">
         <v>-31000000</v>
       </c>
       <c r="L22" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="M22" t="n">
         <v>0.03908855826627113</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="P22" t="n">
-        <v>1629388.312243579</v>
+        <v>190665.3809258619</v>
       </c>
       <c r="Q22" t="n">
-        <v>814694.1561217897</v>
+        <v>95332.69046293097</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I23" t="n">
         <v>2250000</v>
       </c>
       <c r="J23" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K23" t="n">
         <v>-31000000</v>
       </c>
       <c r="L23" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="M23" t="n">
         <v>0.03915884386251234</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="P23" t="n">
-        <v>-115687.3889809956</v>
+        <v>-110207.7521488922</v>
       </c>
       <c r="Q23" t="n">
-        <v>-115687.3889809956</v>
+        <v>-110207.7521488922</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I24" t="n">
         <v>2250000</v>
       </c>
       <c r="J24" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K24" t="n">
         <v>-31000000</v>
       </c>
       <c r="L24" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="M24" t="n">
         <v>0.03922681220647117</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="P24" t="n">
-        <v>-110110.0511051501</v>
+        <v>-76368.57196996707</v>
       </c>
       <c r="Q24" t="n">
-        <v>-110110.0511051501</v>
+        <v>-76368.57196996707</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I25" t="n">
         <v>2250000</v>
       </c>
       <c r="J25" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K25" t="n">
         <v>-31000000</v>
       </c>
       <c r="L25" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="M25" t="n">
         <v>0.03929424848359133</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="P25" t="n">
-        <v>-123655.4519297632</v>
+        <v>-60301.13856132274</v>
       </c>
       <c r="Q25" t="n">
-        <v>-123655.4519297632</v>
+        <v>-60301.13856132274</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J26" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M26" t="n">
         <v>0.03936107056455495</v>
@@ -2974,10 +2974,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="P26" t="n">
-        <v>-78578.86078859412</v>
+        <v>-80987.4201389782</v>
       </c>
       <c r="Q26" t="n">
-        <v>-78578.86078859412</v>
+        <v>-80987.4201389782</v>
       </c>
     </row>
     <row r="27">
@@ -3011,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J27" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K27" t="n">
         <v>-62000000</v>
       </c>
       <c r="L27" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="M27" t="n">
         <v>0.03942868733737526</v>
@@ -3035,10 +3035,10 @@
         <v>-0.02566354060598441</v>
       </c>
       <c r="P27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K28" t="n">
         <v>-620000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="M28" t="n">
         <v>0.03432749872940843</v>
@@ -3096,10 +3096,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="P28" t="n">
-        <v>15429497.47952432</v>
+        <v>15553292.57838485</v>
       </c>
       <c r="Q28" t="n">
-        <v>7714748.739762162</v>
+        <v>7776646.289192423</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J29" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K29" t="n">
         <v>-62000000</v>
       </c>
       <c r="L29" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="M29" t="n">
         <v>0.03782665436246635</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="P29" t="n">
-        <v>-15185169.12173664</v>
+        <v>-15141069.48101515</v>
       </c>
       <c r="Q29" t="n">
-        <v>-15185169.12173664</v>
+        <v>-15141069.48101515</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J30" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M30" t="n">
         <v>0.03830470017405307</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="P30" t="n">
-        <v>-11483953.18878565</v>
+        <v>-11065882.21964725</v>
       </c>
       <c r="Q30" t="n">
-        <v>-11483953.18878565</v>
+        <v>-11065882.21964725</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I31" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J31" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K31" t="n">
         <v>-124000000</v>
       </c>
       <c r="L31" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="M31" t="n">
         <v>0.03852218097221538</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="P31" t="n">
-        <v>-10947375.32069406</v>
+        <v>-13816048.55110825</v>
       </c>
       <c r="Q31" t="n">
-        <v>-10947375.32069406</v>
+        <v>-13816048.55110825</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I32" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J32" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K32" t="n">
         <v>-62000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="M32" t="n">
         <v>0.03873510939427094</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="P32" t="n">
-        <v>2349365.385017809</v>
+        <v>2290536.840539652</v>
       </c>
       <c r="Q32" t="n">
-        <v>1174682.692508904</v>
+        <v>1145268.420269826</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I33" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J33" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K33" t="n">
         <v>-62000000</v>
       </c>
       <c r="L33" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="M33" t="n">
         <v>0.03888939094511485</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="P33" t="n">
-        <v>1724907.605235288</v>
+        <v>1717240.814220452</v>
       </c>
       <c r="Q33" t="n">
-        <v>862453.8026176442</v>
+        <v>858620.4071102258</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J34" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K34" t="n">
         <v>-31000000</v>
       </c>
       <c r="L34" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="M34" t="n">
         <v>0.03901400018340251</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="P34" t="n">
-        <v>-1459706.637583918</v>
+        <v>-358383.9370935452</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1459706.637583918</v>
+        <v>-358383.9370935452</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I35" t="n">
         <v>2250000</v>
       </c>
       <c r="J35" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K35" t="n">
         <v>-31000000</v>
       </c>
       <c r="L35" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="M35" t="n">
         <v>0.03908855826627113</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="P35" t="n">
-        <v>439740.6215403088</v>
+        <v>51456.925574181</v>
       </c>
       <c r="Q35" t="n">
-        <v>219870.3107701544</v>
+        <v>25728.4627870905</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I36" t="n">
         <v>2250000</v>
       </c>
       <c r="J36" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K36" t="n">
         <v>-31000000</v>
       </c>
       <c r="L36" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="M36" t="n">
         <v>0.03915884386251234</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="P36" t="n">
-        <v>-23800.19975011954</v>
+        <v>-22672.88196456904</v>
       </c>
       <c r="Q36" t="n">
-        <v>-23800.19975011954</v>
+        <v>-22672.88196456904</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I37" t="n">
         <v>2250000</v>
       </c>
       <c r="J37" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K37" t="n">
         <v>-31000000</v>
       </c>
       <c r="L37" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="M37" t="n">
         <v>0.03922681220647117</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="P37" t="n">
-        <v>-16073.06334116399</v>
+        <v>-11147.72795242223</v>
       </c>
       <c r="Q37" t="n">
-        <v>-16073.06334116399</v>
+        <v>-11147.72795242223</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I38" t="n">
         <v>2250000</v>
       </c>
       <c r="J38" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K38" t="n">
         <v>-31000000</v>
       </c>
       <c r="L38" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="M38" t="n">
         <v>0.03929424848359133</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="P38" t="n">
-        <v>-11250.80366190433</v>
+        <v>-5486.505123349388</v>
       </c>
       <c r="Q38" t="n">
-        <v>-11250.80366190433</v>
+        <v>-5486.505123349388</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J39" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M39" t="n">
         <v>0.03936107056455495</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="P39" t="n">
-        <v>-3159.178560060345</v>
+        <v>-3256.01209752836</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3159.178560060345</v>
+        <v>-3256.01209752836</v>
       </c>
     </row>
     <row r="40">
@@ -3804,19 +3804,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J40" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K40" t="n">
         <v>-62000000</v>
       </c>
       <c r="L40" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="M40" t="n">
         <v>0.03942868733737526</v>
@@ -3828,10 +3828,10 @@
         <v>0.0001712813743293129</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K41" t="n">
         <v>-620000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="M41" t="n">
         <v>0.03432749872940843</v>
@@ -3889,10 +3889,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="P41" t="n">
-        <v>-36247659.17335165</v>
+        <v>-36400113.47886805</v>
       </c>
       <c r="Q41" t="n">
-        <v>-36247659.17335165</v>
+        <v>-36400113.47886805</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J42" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K42" t="n">
         <v>-62000000</v>
       </c>
       <c r="L42" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="M42" t="n">
         <v>0.03782665436246635</v>
@@ -3950,10 +3950,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="P42" t="n">
-        <v>17642871.74051509</v>
+        <v>17587520.64685568</v>
       </c>
       <c r="Q42" t="n">
-        <v>8821435.870257543</v>
+        <v>8793760.323427841</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J43" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M43" t="n">
         <v>0.03830470017405307</v>
@@ -4011,10 +4011,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="P43" t="n">
-        <v>14740223.1984997</v>
+        <v>14203608.38506325</v>
       </c>
       <c r="Q43" t="n">
-        <v>7370111.599249849</v>
+        <v>7101804.192531625</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I44" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J44" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K44" t="n">
         <v>-124000000</v>
       </c>
       <c r="L44" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="M44" t="n">
         <v>0.03852218097221538</v>
@@ -4072,10 +4072,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="P44" t="n">
-        <v>12603538.27983324</v>
+        <v>16382250.36081849</v>
       </c>
       <c r="Q44" t="n">
-        <v>6301769.139916618</v>
+        <v>8191125.180409247</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I45" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J45" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K45" t="n">
         <v>-62000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="M45" t="n">
         <v>0.03873510939427094</v>
@@ -4133,10 +4133,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="P45" t="n">
-        <v>-3902076.660081655</v>
+        <v>-3822103.415648551</v>
       </c>
       <c r="Q45" t="n">
-        <v>-3902076.660081655</v>
+        <v>-3822103.415648551</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I46" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J46" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K46" t="n">
         <v>-62000000</v>
       </c>
       <c r="L46" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="M46" t="n">
         <v>0.03888939094511485</v>
@@ -4194,10 +4194,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="P46" t="n">
-        <v>-2978372.895632596</v>
+        <v>-2967529.679335522</v>
       </c>
       <c r="Q46" t="n">
-        <v>-2978372.895632596</v>
+        <v>-2967529.679335522</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J47" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K47" t="n">
         <v>-31000000</v>
       </c>
       <c r="L47" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="M47" t="n">
         <v>0.03901400018340251</v>
@@ -4255,10 +4255,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="P47" t="n">
-        <v>1972311.876162619</v>
+        <v>334098.562381001</v>
       </c>
       <c r="Q47" t="n">
-        <v>986155.9380813093</v>
+        <v>167049.2811905005</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I48" t="n">
         <v>2250000</v>
       </c>
       <c r="J48" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K48" t="n">
         <v>-31000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="M48" t="n">
         <v>0.03908855826627113</v>
@@ -4316,10 +4316,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="P48" t="n">
-        <v>-841367.9283942515</v>
+        <v>-222903.7581030664</v>
       </c>
       <c r="Q48" t="n">
-        <v>-841367.9283942515</v>
+        <v>-222903.7581030664</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I49" t="n">
         <v>2250000</v>
       </c>
       <c r="J49" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K49" t="n">
         <v>-31000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="M49" t="n">
         <v>0.03915884386251234</v>
@@ -4377,10 +4377,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="P49" t="n">
-        <v>-52992.93061580981</v>
+        <v>-54965.74260521386</v>
       </c>
       <c r="Q49" t="n">
-        <v>-52992.93061580981</v>
+        <v>-54965.74260521386</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I50" t="n">
         <v>2250000</v>
       </c>
       <c r="J50" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K50" t="n">
         <v>-31000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="M50" t="n">
         <v>0.03922681220647117</v>
@@ -4438,10 +4438,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="P50" t="n">
-        <v>-25810.93439611698</v>
+        <v>-35766.3135039513</v>
       </c>
       <c r="Q50" t="n">
-        <v>-25810.93439611698</v>
+        <v>-35766.3135039513</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I51" t="n">
         <v>2250000</v>
       </c>
       <c r="J51" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K51" t="n">
         <v>-31000000</v>
       </c>
       <c r="L51" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="M51" t="n">
         <v>0.03929424848359133</v>
@@ -4499,10 +4499,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="P51" t="n">
-        <v>-1967.060839978806</v>
+        <v>-16873.10949510173</v>
       </c>
       <c r="Q51" t="n">
-        <v>-1967.060839978806</v>
+        <v>-16873.10949510173</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J52" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M52" t="n">
         <v>0.03936107056455495</v>
@@ -4560,10 +4560,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="P52" t="n">
-        <v>14156.74786704356</v>
+        <v>14590.67331600027</v>
       </c>
       <c r="Q52" t="n">
-        <v>7078.373933521779</v>
+        <v>7295.336658000136</v>
       </c>
     </row>
     <row r="53">
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J53" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K53" t="n">
         <v>-62000000</v>
       </c>
       <c r="L53" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="M53" t="n">
         <v>0.03942868733737526</v>
@@ -4621,10 +4621,10 @@
         <v>0.003319954993421748</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="54">
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K54" t="n">
         <v>-620000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="M54" t="n">
         <v>0.03432749872940843</v>
@@ -4682,10 +4682,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="P54" t="n">
-        <v>-45364612.96823002</v>
+        <v>-45555412.33908088</v>
       </c>
       <c r="Q54" t="n">
-        <v>-45364612.96823002</v>
+        <v>-45555412.33908088</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J55" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K55" t="n">
         <v>-62000000</v>
       </c>
       <c r="L55" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="M55" t="n">
         <v>0.03782665436246635</v>
@@ -4743,10 +4743,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="P55" t="n">
-        <v>22870100.86768048</v>
+        <v>22798350.35485325</v>
       </c>
       <c r="Q55" t="n">
-        <v>11435050.43384024</v>
+        <v>11399175.17742662</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J56" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M56" t="n">
         <v>0.03830470017405307</v>
@@ -4804,10 +4804,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="P56" t="n">
-        <v>19901104.94179668</v>
+        <v>19176609.28310079</v>
       </c>
       <c r="Q56" t="n">
-        <v>9950552.470898338</v>
+        <v>9588304.641550394</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I57" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J57" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K57" t="n">
         <v>-124000000</v>
       </c>
       <c r="L57" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="M57" t="n">
         <v>0.03852218097221538</v>
@@ -4865,10 +4865,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="P57" t="n">
-        <v>17807135.32507474</v>
+        <v>23145956.52644055</v>
       </c>
       <c r="Q57" t="n">
-        <v>8903567.662537372</v>
+        <v>11572978.26322027</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I58" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J58" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K58" t="n">
         <v>-62000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="M58" t="n">
         <v>0.03873510939427094</v>
@@ -4926,10 +4926,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="P58" t="n">
-        <v>-5807923.526519679</v>
+        <v>-5688889.861039254</v>
       </c>
       <c r="Q58" t="n">
-        <v>-5807923.526519679</v>
+        <v>-5688889.861039254</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I59" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J59" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K59" t="n">
         <v>-62000000</v>
       </c>
       <c r="L59" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="M59" t="n">
         <v>0.03888939094511485</v>
@@ -4987,10 +4987,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="P59" t="n">
-        <v>-4708401.366710636</v>
+        <v>-4691259.720509267</v>
       </c>
       <c r="Q59" t="n">
-        <v>-4708401.366710636</v>
+        <v>-4691259.720509267</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J60" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K60" t="n">
         <v>-31000000</v>
       </c>
       <c r="L60" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="M60" t="n">
         <v>0.03901400018340251</v>
@@ -5048,10 +5048,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="P60" t="n">
-        <v>3342151.380328503</v>
+        <v>566141.6862732342</v>
       </c>
       <c r="Q60" t="n">
-        <v>1671075.690164251</v>
+        <v>283070.8431366171</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I61" t="n">
         <v>2250000</v>
       </c>
       <c r="J61" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K61" t="n">
         <v>-31000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="M61" t="n">
         <v>0.03908855826627113</v>
@@ -5109,10 +5109,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="P61" t="n">
-        <v>-1547906.949221786</v>
+        <v>-410087.2692329567</v>
       </c>
       <c r="Q61" t="n">
-        <v>-1547906.949221786</v>
+        <v>-410087.2692329567</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I62" t="n">
         <v>2250000</v>
       </c>
       <c r="J62" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K62" t="n">
         <v>-31000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="M62" t="n">
         <v>0.03915884386251234</v>
@@ -5170,10 +5170,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="P62" t="n">
-        <v>-107314.4696357043</v>
+        <v>-111309.5548267598</v>
       </c>
       <c r="Q62" t="n">
-        <v>-107314.4696357043</v>
+        <v>-111309.5548267598</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I63" t="n">
         <v>2250000</v>
       </c>
       <c r="J63" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K63" t="n">
         <v>-31000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="M63" t="n">
         <v>0.03922681220647117</v>
@@ -5231,10 +5231,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="P63" t="n">
-        <v>-58750.7762209344</v>
+        <v>-81411.18212421431</v>
       </c>
       <c r="Q63" t="n">
-        <v>-58750.7762209344</v>
+        <v>-81411.18212421431</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I64" t="n">
         <v>2250000</v>
       </c>
       <c r="J64" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K64" t="n">
         <v>-31000000</v>
       </c>
       <c r="L64" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="M64" t="n">
         <v>0.03929424848359133</v>
@@ -5292,10 +5292,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="P64" t="n">
-        <v>-5172.460789406253</v>
+        <v>-44368.47884161649</v>
       </c>
       <c r="Q64" t="n">
-        <v>-5172.460789406253</v>
+        <v>-44368.47884161649</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J65" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M65" t="n">
         <v>0.03936107056455495</v>
@@ -5353,10 +5353,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="P65" t="n">
-        <v>44779.14269957671</v>
+        <v>46151.69024950127</v>
       </c>
       <c r="Q65" t="n">
-        <v>22389.57134978836</v>
+        <v>23075.84512475063</v>
       </c>
     </row>
     <row r="66">
@@ -5390,19 +5390,19 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J66" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K66" t="n">
         <v>-62000000</v>
       </c>
       <c r="L66" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="M66" t="n">
         <v>0.03942868733737526</v>
@@ -5414,10 +5414,10 @@
         <v>0.01346967956071188</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="67">
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K67" t="n">
         <v>-620000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="M67" t="n">
         <v>0.03432749872940843</v>
@@ -5475,10 +5475,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="P67" t="n">
-        <v>23382381.53250516</v>
+        <v>23569984.80586207</v>
       </c>
       <c r="Q67" t="n">
-        <v>11691190.76625258</v>
+        <v>11784992.40293104</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J68" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K68" t="n">
         <v>-62000000</v>
       </c>
       <c r="L68" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="M68" t="n">
         <v>0.03782665436246635</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="P68" t="n">
-        <v>-24638913.08788164</v>
+        <v>-24567358.5858387</v>
       </c>
       <c r="Q68" t="n">
-        <v>-24638913.08788164</v>
+        <v>-24567358.5858387</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J69" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M69" t="n">
         <v>0.03830470017405307</v>
@@ -5597,10 +5597,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="P69" t="n">
-        <v>-19801670.62805112</v>
+        <v>-19080794.85522814</v>
       </c>
       <c r="Q69" t="n">
-        <v>-19801670.62805112</v>
+        <v>-19080794.85522814</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I70" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J70" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K70" t="n">
         <v>-124000000</v>
       </c>
       <c r="L70" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="M70" t="n">
         <v>0.03852218097221538</v>
@@ -5658,10 +5658,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="P70" t="n">
-        <v>-20234950.91453646</v>
+        <v>-25537359.96755828</v>
       </c>
       <c r="Q70" t="n">
-        <v>-20234950.91453646</v>
+        <v>-25537359.96755828</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I71" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J71" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K71" t="n">
         <v>-62000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="M71" t="n">
         <v>0.03873510939427094</v>
@@ -5719,10 +5719,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="P71" t="n">
-        <v>4714088.637765296</v>
+        <v>4596046.984955874</v>
       </c>
       <c r="Q71" t="n">
-        <v>2357044.318882648</v>
+        <v>2298023.492477937</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I72" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J72" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K72" t="n">
         <v>-62000000</v>
       </c>
       <c r="L72" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="M72" t="n">
         <v>0.03888939094511485</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="P72" t="n">
-        <v>3819603.605249374</v>
+        <v>3802626.404550575</v>
       </c>
       <c r="Q72" t="n">
-        <v>1909801.802624687</v>
+        <v>1901313.202275287</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J73" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K73" t="n">
         <v>-31000000</v>
       </c>
       <c r="L73" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="M73" t="n">
         <v>0.03901400018340251</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="P73" t="n">
-        <v>-3640472.141650804</v>
+        <v>-893800.6483026487</v>
       </c>
       <c r="Q73" t="n">
-        <v>-3640472.141650804</v>
+        <v>-893800.6483026487</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I74" t="n">
         <v>2250000</v>
       </c>
       <c r="J74" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K74" t="n">
         <v>-31000000</v>
       </c>
       <c r="L74" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="M74" t="n">
         <v>0.03908855826627113</v>
@@ -5902,10 +5902,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="P74" t="n">
-        <v>1273911.216587889</v>
+        <v>149068.6815115365</v>
       </c>
       <c r="Q74" t="n">
-        <v>636955.6082939446</v>
+        <v>74534.34075576825</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I75" t="n">
         <v>2250000</v>
       </c>
       <c r="J75" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K75" t="n">
         <v>-31000000</v>
       </c>
       <c r="L75" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="M75" t="n">
         <v>0.03915884386251234</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="P75" t="n">
-        <v>-83339.80282946698</v>
+        <v>-79392.33839806204</v>
       </c>
       <c r="Q75" t="n">
-        <v>-83339.80282946698</v>
+        <v>-79392.33839806204</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I76" t="n">
         <v>2250000</v>
       </c>
       <c r="J76" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K76" t="n">
         <v>-31000000</v>
       </c>
       <c r="L76" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="M76" t="n">
         <v>0.03922681220647117</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="P76" t="n">
-        <v>-73035.67850163192</v>
+        <v>-50655.0529587973</v>
       </c>
       <c r="Q76" t="n">
-        <v>-73035.67850163192</v>
+        <v>-50655.0529587973</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I77" t="n">
         <v>2250000</v>
       </c>
       <c r="J77" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K77" t="n">
         <v>-31000000</v>
       </c>
       <c r="L77" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="M77" t="n">
         <v>0.03929424848359133</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="P77" t="n">
-        <v>-75538.78426041281</v>
+        <v>-36836.82866670786</v>
       </c>
       <c r="Q77" t="n">
-        <v>-75538.78426041281</v>
+        <v>-36836.82866670786</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J78" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M78" t="n">
         <v>0.03936107056455495</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="P78" t="n">
-        <v>-44208.17843833612</v>
+        <v>-45563.22508157478</v>
       </c>
       <c r="Q78" t="n">
-        <v>-44208.17843833612</v>
+        <v>-45563.22508157478</v>
       </c>
     </row>
     <row r="79">
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J79" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K79" t="n">
         <v>-62000000</v>
       </c>
       <c r="L79" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="M79" t="n">
         <v>0.03942868733737526</v>
@@ -6207,10 +6207,10 @@
         <v>-0.01329726695768341</v>
       </c>
       <c r="P79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="K80" t="n">
         <v>-620000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="M80" t="n">
         <v>0.03432749872940843</v>
@@ -6268,10 +6268,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="P80" t="n">
-        <v>6813323.240446202</v>
+        <v>6867988.405351218</v>
       </c>
       <c r="Q80" t="n">
-        <v>3406661.620223101</v>
+        <v>3433994.202675609</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="I81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J81" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="K81" t="n">
         <v>-62000000</v>
       </c>
       <c r="L81" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="M81" t="n">
         <v>0.03782665436246635</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="P81" t="n">
-        <v>-7666820.325395201</v>
+        <v>-7644554.915038845</v>
       </c>
       <c r="Q81" t="n">
-        <v>-7666820.325395201</v>
+        <v>-7644554.915038845</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="I82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J82" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="M82" t="n">
         <v>0.03830470017405307</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="P82" t="n">
-        <v>-6704096.256018637</v>
+        <v>-6460035.001773206</v>
       </c>
       <c r="Q82" t="n">
-        <v>-6704096.256018637</v>
+        <v>-6460035.001773206</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="I83" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J83" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="K83" t="n">
         <v>-124000000</v>
       </c>
       <c r="L83" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="M83" t="n">
         <v>0.03852218097221538</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="P83" t="n">
-        <v>-7443371.129805716</v>
+        <v>-9393847.739824571</v>
       </c>
       <c r="Q83" t="n">
-        <v>-7443371.129805716</v>
+        <v>-9393847.739824571</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="I84" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J84" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="K84" t="n">
         <v>-62000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="M84" t="n">
         <v>0.03873510939427094</v>
@@ -6512,10 +6512,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="P84" t="n">
-        <v>1884708.697958241</v>
+        <v>1837515.243005143</v>
       </c>
       <c r="Q84" t="n">
-        <v>942354.3489791203</v>
+        <v>918757.6215025715</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="I85" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J85" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="K85" t="n">
         <v>-62000000</v>
       </c>
       <c r="L85" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="M85" t="n">
         <v>0.03888939094511485</v>
@@ -6573,10 +6573,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="P85" t="n">
-        <v>1660496.393620498</v>
+        <v>1653115.894634848</v>
       </c>
       <c r="Q85" t="n">
-        <v>830248.196810249</v>
+        <v>826557.9473174242</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="I86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J86" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="K86" t="n">
         <v>-31000000</v>
       </c>
       <c r="L86" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="M86" t="n">
         <v>0.03901400018340251</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="P86" t="n">
-        <v>-1719918.128105035</v>
+        <v>-422270.4852867442</v>
       </c>
       <c r="Q86" t="n">
-        <v>-1719918.128105035</v>
+        <v>-422270.4852867442</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="I87" t="n">
         <v>2250000</v>
       </c>
       <c r="J87" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="K87" t="n">
         <v>-31000000</v>
       </c>
       <c r="L87" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="M87" t="n">
         <v>0.03908855826627113</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="P87" t="n">
-        <v>654574.397627883</v>
+        <v>76596.03050434779</v>
       </c>
       <c r="Q87" t="n">
-        <v>327287.1988139415</v>
+        <v>38298.01525217389</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="I88" t="n">
         <v>2250000</v>
       </c>
       <c r="J88" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="K88" t="n">
         <v>-31000000</v>
       </c>
       <c r="L88" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="M88" t="n">
         <v>0.03915884386251234</v>
@@ -6756,10 +6756,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="P88" t="n">
-        <v>-46506.17081976515</v>
+        <v>-44303.36437051645</v>
       </c>
       <c r="Q88" t="n">
-        <v>-46506.17081976515</v>
+        <v>-44303.36437051645</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="I89" t="n">
         <v>2250000</v>
       </c>
       <c r="J89" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="K89" t="n">
         <v>-31000000</v>
       </c>
       <c r="L89" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="M89" t="n">
         <v>0.03922681220647117</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="P89" t="n">
-        <v>-44291.34685461532</v>
+        <v>-30718.96594329398</v>
       </c>
       <c r="Q89" t="n">
-        <v>-44291.34685461532</v>
+        <v>-30718.96594329398</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="I90" t="n">
         <v>2250000</v>
       </c>
       <c r="J90" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="K90" t="n">
         <v>-31000000</v>
       </c>
       <c r="L90" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="M90" t="n">
         <v>0.03929424848359133</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="P90" t="n">
-        <v>-49771.27784650621</v>
+        <v>-24271.18800634034</v>
       </c>
       <c r="Q90" t="n">
-        <v>-49771.27784650621</v>
+        <v>-24271.18800634034</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="I91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J91" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="M91" t="n">
         <v>0.03936107056455495</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="P91" t="n">
-        <v>-31647.74542077571</v>
+        <v>-32617.79604745581</v>
       </c>
       <c r="Q91" t="n">
-        <v>-31647.74542077571</v>
+        <v>-32617.79604745581</v>
       </c>
     </row>
     <row r="92">
@@ -6976,19 +6976,19 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="I92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J92" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="K92" t="n">
         <v>-62000000</v>
       </c>
       <c r="L92" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="M92" t="n">
         <v>0.03942868733737526</v>
@@ -7000,10 +7000,10 @@
         <v>-0.01034243719640493</v>
       </c>
       <c r="P92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33204891.25999999</v>
+        <v>35717002.64000005</v>
       </c>
       <c r="D2" t="n">
-        <v>16602445.63</v>
+        <v>17858501.32000002</v>
       </c>
       <c r="E2" t="n">
-        <v>2.767074271666666</v>
+        <v>2.97641688666667</v>
       </c>
       <c r="F2" t="n">
-        <v>1.383537135833333</v>
+        <v>1.488208443333335</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-36949558.86999995</v>
+        <v>-39402456.87</v>
       </c>
       <c r="D3" t="n">
-        <v>-36949558.86999995</v>
+        <v>-39402456.87</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.079129905833329</v>
+        <v>-3.2835380725</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.079129905833329</v>
+        <v>-3.2835380725</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24037176.79000008</v>
+        <v>24954858.69</v>
       </c>
       <c r="D4" t="n">
-        <v>12018588.39500004</v>
+        <v>12477429.345</v>
       </c>
       <c r="E4" t="n">
-        <v>2.00309806583334</v>
+        <v>2.0795715575</v>
       </c>
       <c r="F4" t="n">
-        <v>1.00154903291667</v>
+        <v>1.03978577875</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-25108557.89999998</v>
+        <v>-25784012.27999997</v>
       </c>
       <c r="D5" t="n">
-        <v>-25108557.89999998</v>
+        <v>-25784012.27999997</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.092379824999998</v>
+        <v>-2.148667689999998</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.092379824999998</v>
+        <v>-2.148667689999998</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-8558612.109999955</v>
+        <v>-8155775.48999995</v>
       </c>
       <c r="D6" t="n">
-        <v>-8558612.109999955</v>
+        <v>-8155775.48999995</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7132176758333296</v>
+        <v>-0.6796479574999958</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7132176758333296</v>
+        <v>-0.6796479574999958</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4684805.470000029</v>
+        <v>4659880.629999995</v>
       </c>
       <c r="D7" t="n">
-        <v>2342402.735000014</v>
+        <v>2329940.314999998</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3904004558333357</v>
+        <v>0.3883233858333329</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1952002279166679</v>
+        <v>0.1941616929166665</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-15844724.27999997</v>
+        <v>-16848137.46999997</v>
       </c>
       <c r="D8" t="n">
-        <v>-15844724.27999997</v>
+        <v>-16848137.46999997</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.320393689999998</v>
+        <v>-1.404011455833331</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.320393689999998</v>
+        <v>-1.404011455833331</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="F2" t="n">
         <v>-620000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J2" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="K2" t="n">
-        <v>-13050005.93185206</v>
+        <v>-12850337.93889425</v>
       </c>
       <c r="L2" t="n">
-        <v>6866992.233221918</v>
+        <v>6667324.24026411</v>
       </c>
       <c r="M2" t="n">
-        <v>-13050005.93185206</v>
+        <v>-12850337.93889425</v>
       </c>
       <c r="N2" t="n">
-        <v>6866992.233221918</v>
+        <v>6667324.24026411</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="F3" t="n">
         <v>-62000000</v>
       </c>
       <c r="G3" t="n">
-        <v>921293400.75</v>
+        <v>1117062051.07</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J3" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="K3" t="n">
-        <v>7876856.173541667</v>
+        <v>9671402.13480833</v>
       </c>
       <c r="L3" t="n">
-        <v>-8445189.506874999</v>
+        <v>-10239735.46814166</v>
       </c>
       <c r="M3" t="n">
-        <v>7056047.073085045</v>
+        <v>8850593.03435171</v>
       </c>
       <c r="N3" t="n">
-        <v>-7624380.406418378</v>
+        <v>-9418926.367685042</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J4" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K4" t="n">
-        <v>6849605.095833334</v>
+        <v>7066364.445250001</v>
       </c>
       <c r="L4" t="n">
-        <v>-6849605.095833334</v>
+        <v>-7066364.445250001</v>
       </c>
       <c r="M4" t="n">
-        <v>6425148.817294521</v>
+        <v>6641908.166711188</v>
       </c>
       <c r="N4" t="n">
-        <v>-6425148.817294521</v>
+        <v>-6641908.166711188</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="F5" t="n">
         <v>-124000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1372487704.21</v>
+        <v>1063311463.01</v>
       </c>
       <c r="H5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J5" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="K5" t="n">
-        <v>9363657.781574998</v>
+        <v>7044835.972575</v>
       </c>
       <c r="L5" t="n">
-        <v>-10293657.781575</v>
+        <v>-7974835.972575</v>
       </c>
       <c r="M5" t="n">
-        <v>8386311.124040753</v>
+        <v>6067489.315040753</v>
       </c>
       <c r="N5" t="n">
-        <v>-9316311.124040753</v>
+        <v>-6997489.315040753</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="F6" t="n">
         <v>-62000000</v>
       </c>
       <c r="G6" t="n">
-        <v>-182620576.92</v>
+        <v>-381326776.01</v>
       </c>
       <c r="H6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J6" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="K6" t="n">
-        <v>-1630803.846133334</v>
+        <v>-2955511.840066667</v>
       </c>
       <c r="L6" t="n">
-        <v>1217470.5128</v>
+        <v>2542178.506733334</v>
       </c>
       <c r="M6" t="n">
-        <v>-2230475.736544293</v>
+        <v>-3555183.730477626</v>
       </c>
       <c r="N6" t="n">
-        <v>1817142.403210959</v>
+        <v>3141850.397144292</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="F7" t="n">
         <v>-62000000</v>
       </c>
       <c r="G7" t="n">
-        <v>-189489410.97</v>
+        <v>-231429918.6</v>
       </c>
       <c r="H7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J7" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="K7" t="n">
-        <v>-1467021.563991667</v>
+        <v>-1711674.525166667</v>
       </c>
       <c r="L7" t="n">
-        <v>1105354.897325</v>
+        <v>1350007.8585</v>
       </c>
       <c r="M7" t="n">
-        <v>-1991866.700977968</v>
+        <v>-2236519.662152968</v>
       </c>
       <c r="N7" t="n">
-        <v>1630200.034311301</v>
+        <v>1874852.995486301</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="F8" t="n">
         <v>-31000000</v>
       </c>
       <c r="G8" t="n">
-        <v>173015112.97</v>
+        <v>328664448.81</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J8" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="K8" t="n">
-        <v>710075.5648500002</v>
+        <v>1488322.24405</v>
       </c>
       <c r="L8" t="n">
-        <v>-865075.5648500002</v>
+        <v>-1643322.24405</v>
       </c>
       <c r="M8" t="n">
-        <v>260232.5237541097</v>
+        <v>1038479.20295411</v>
       </c>
       <c r="N8" t="n">
-        <v>-415232.5237541097</v>
+        <v>-1193479.20295411</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="F9" t="n">
         <v>-31000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-20277242.50999999</v>
+        <v>88779553.03</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="K9" t="n">
-        <v>-213655.177125</v>
+        <v>240748.137625</v>
       </c>
       <c r="L9" t="n">
-        <v>84488.51045833329</v>
+        <v>-369914.8042916666</v>
       </c>
       <c r="M9" t="n">
-        <v>-204280.177125</v>
+        <v>250123.137625</v>
       </c>
       <c r="N9" t="n">
-        <v>75113.51045833329</v>
+        <v>-379289.8042916666</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="F10" t="n">
         <v>-31000000</v>
       </c>
       <c r="G10" t="n">
-        <v>10746230.59999999</v>
+        <v>12899273.93</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J10" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="K10" t="n">
-        <v>-67512.5646666667</v>
+        <v>-60335.75356666668</v>
       </c>
       <c r="L10" t="n">
-        <v>-35820.76866666665</v>
+        <v>-42997.57976666667</v>
       </c>
       <c r="M10" t="n">
-        <v>-60012.5646666667</v>
+        <v>-52835.75356666667</v>
       </c>
       <c r="N10" t="n">
-        <v>-43320.76866666665</v>
+        <v>-50497.57976666667</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="F11" t="n">
         <v>-31000000</v>
       </c>
       <c r="G11" t="n">
-        <v>9731487.229999997</v>
+        <v>9059584</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J11" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="K11" t="n">
-        <v>-53171.28192500001</v>
+        <v>-54851.04</v>
       </c>
       <c r="L11" t="n">
-        <v>-24328.71807499999</v>
+        <v>-22648.96</v>
       </c>
       <c r="M11" t="n">
-        <v>-47546.28192500001</v>
+        <v>-49226.04</v>
       </c>
       <c r="N11" t="n">
-        <v>-29953.71807499999</v>
+        <v>-28273.96</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="F12" t="n">
         <v>-31000000</v>
       </c>
       <c r="G12" t="n">
-        <v>11909921.49</v>
+        <v>10483816.3</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J12" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="K12" t="n">
-        <v>-31816.79751666665</v>
+        <v>-34193.6395</v>
       </c>
       <c r="L12" t="n">
-        <v>-19849.86915</v>
+        <v>-17473.02716666666</v>
       </c>
       <c r="M12" t="n">
-        <v>-28066.79751666666</v>
+        <v>-30443.6395</v>
       </c>
       <c r="N12" t="n">
-        <v>-23599.86915</v>
+        <v>-21223.02716666666</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J13" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K13" t="n">
-        <v>29741.23346666668</v>
+        <v>101552.1519250001</v>
       </c>
       <c r="L13" t="n">
-        <v>-29741.23346666668</v>
+        <v>-101552.1519250001</v>
       </c>
       <c r="M13" t="n">
-        <v>31626.50743926942</v>
+        <v>103437.4258976028</v>
       </c>
       <c r="N13" t="n">
-        <v>-31626.50743926942</v>
+        <v>-103437.4258976028</v>
       </c>
     </row>
     <row r="14">
@@ -1087,22 +1087,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="F14" t="n">
         <v>-62000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-17556538.55</v>
+        <v>-17196736.40000001</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J14" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="K14" t="n">
         <v>-0</v>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8315948.686056274</v>
+        <v>7946320.349039084</v>
       </c>
       <c r="C2" t="n">
-        <v>-17288962.38468641</v>
+        <v>-16919334.04766922</v>
       </c>
       <c r="D2" t="n">
-        <v>4547111.855006047</v>
+        <v>4177483.517988857</v>
       </c>
       <c r="E2" t="n">
-        <v>-13520125.55363619</v>
+        <v>-13150497.21661899</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-44992749.09</v>
+        <v>-45534720.79</v>
       </c>
       <c r="D2" t="n">
-        <v>-70505634.63268048</v>
+        <v>-71131406.49216403</v>
       </c>
       <c r="E2" t="n">
-        <v>-115498383.7226805</v>
+        <v>-116666127.282164</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60616755.16</v>
+        <v>70547343.11</v>
       </c>
       <c r="D3" t="n">
-        <v>7656881.216315068</v>
+        <v>6860671.899068493</v>
       </c>
       <c r="E3" t="n">
-        <v>68273636.37631507</v>
+        <v>77408015.00906849</v>
       </c>
     </row>
     <row r="4">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>459987425.03</v>
+        <v>458424337.93</v>
       </c>
       <c r="D5" t="n">
-        <v>46495852.15232349</v>
+        <v>47014078.12966713</v>
       </c>
       <c r="E5" t="n">
-        <v>506483277.1823235</v>
+        <v>505438416.0596671</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>478935731.8</v>
+        <v>486761260.95</v>
       </c>
       <c r="C2" t="n">
-        <v>-16352901.26404192</v>
+        <v>-17256656.46342841</v>
       </c>
       <c r="D2" t="n">
-        <v>462582830.5359581</v>
+        <v>469504604.4865716</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K2" t="n">
         <v>-620000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="M2" t="n">
         <v>0.03432749872940843</v>
@@ -1510,10 +1510,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="P2" t="n">
-        <v>-32631303.37430746</v>
+        <v>-32132037.17578087</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32631303.37430746</v>
+        <v>-32132037.17578087</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J3" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K3" t="n">
         <v>-62000000</v>
       </c>
       <c r="L3" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="M3" t="n">
         <v>0.03782665436246635</v>
@@ -1571,10 +1571,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="P3" t="n">
-        <v>17714781.8447465</v>
+        <v>22220135.88858093</v>
       </c>
       <c r="Q3" t="n">
-        <v>8857390.922373248</v>
+        <v>11110067.94429046</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J4" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M4" t="n">
         <v>0.03830470017405307</v>
@@ -1632,10 +1632,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="P4" t="n">
-        <v>16199877.06434811</v>
+        <v>16746397.45056022</v>
       </c>
       <c r="Q4" t="n">
-        <v>8099938.532174057</v>
+        <v>8373198.72528011</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J5" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K5" t="n">
         <v>-124000000</v>
       </c>
       <c r="L5" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="M5" t="n">
         <v>0.03852218097221538</v>
@@ -1693,10 +1693,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="P5" t="n">
-        <v>21234360.61087049</v>
+        <v>15363042.72671686</v>
       </c>
       <c r="Q5" t="n">
-        <v>10617180.30543524</v>
+        <v>7681521.363358428</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J6" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K6" t="n">
         <v>-62000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="M6" t="n">
         <v>0.03873510939427094</v>
@@ -1754,10 +1754,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="P6" t="n">
-        <v>-5671815.360242249</v>
+        <v>-9040378.857582752</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5671815.360242249</v>
+        <v>-9040378.857582752</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J7" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K7" t="n">
         <v>-62000000</v>
       </c>
       <c r="L7" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="M7" t="n">
         <v>0.03888939094511485</v>
@@ -1815,10 +1815,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="P7" t="n">
-        <v>-5086871.529461038</v>
+        <v>-5711671.463205808</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5086871.529461038</v>
+        <v>-5711671.463205808</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J8" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K8" t="n">
         <v>-31000000</v>
       </c>
       <c r="L8" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="M8" t="n">
         <v>0.03901400018340251</v>
@@ -1876,10 +1876,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="P8" t="n">
-        <v>667437.9128207581</v>
+        <v>2663465.66420105</v>
       </c>
       <c r="Q8" t="n">
-        <v>333718.956410379</v>
+        <v>1331732.832100525</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I9" t="n">
         <v>2250000</v>
       </c>
       <c r="J9" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K9" t="n">
         <v>-31000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="M9" t="n">
         <v>0.03908855826627113</v>
@@ -1937,10 +1937,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="P9" t="n">
-        <v>-526190.7388415849</v>
+        <v>644274.3512393761</v>
       </c>
       <c r="Q9" t="n">
-        <v>-526190.7388415849</v>
+        <v>322137.1756196881</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I10" t="n">
         <v>2250000</v>
       </c>
       <c r="J10" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K10" t="n">
         <v>-31000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="M10" t="n">
         <v>0.03915884386251234</v>
@@ -1998,10 +1998,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="P10" t="n">
-        <v>-155238.837347826</v>
+        <v>-136674.061501014</v>
       </c>
       <c r="Q10" t="n">
-        <v>-155238.837347826</v>
+        <v>-136674.061501014</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I11" t="n">
         <v>2250000</v>
       </c>
       <c r="J11" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K11" t="n">
         <v>-31000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="M11" t="n">
         <v>0.03922681220647117</v>
@@ -2059,10 +2059,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="P11" t="n">
-        <v>-123518.1300839188</v>
+        <v>-127881.890361634</v>
       </c>
       <c r="Q11" t="n">
-        <v>-123518.1300839188</v>
+        <v>-127881.890361634</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I12" t="n">
         <v>2250000</v>
       </c>
       <c r="J12" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K12" t="n">
         <v>-31000000</v>
       </c>
       <c r="L12" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="M12" t="n">
         <v>0.03929424848359133</v>
@@ -2120,10 +2120,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="P12" t="n">
-        <v>-73224.96182435016</v>
+        <v>-79426.03137597056</v>
       </c>
       <c r="Q12" t="n">
-        <v>-73224.96182435016</v>
+        <v>-79426.03137597056</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J13" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M13" t="n">
         <v>0.03936107056455495</v>
@@ -2181,10 +2181,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="P13" t="n">
-        <v>82865.02185148366</v>
+        <v>271017.7395883861</v>
       </c>
       <c r="Q13" t="n">
-        <v>41432.51092574183</v>
+        <v>135508.869794193</v>
       </c>
     </row>
     <row r="14">
@@ -2218,19 +2218,19 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J14" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K14" t="n">
         <v>-62000000</v>
       </c>
       <c r="L14" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="M14" t="n">
         <v>0.03942868733737526</v>
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K15" t="n">
         <v>-620000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="M15" t="n">
         <v>0.03432749872940843</v>
@@ -2303,10 +2303,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="P15" t="n">
-        <v>17167479.74867882</v>
+        <v>16668309.79054502</v>
       </c>
       <c r="Q15" t="n">
-        <v>8583739.874339411</v>
+        <v>8334154.895272509</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J16" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K16" t="n">
         <v>-62000000</v>
       </c>
       <c r="L16" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="M16" t="n">
         <v>0.03782665436246635</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="P16" t="n">
-        <v>-19100409.08687521</v>
+        <v>-23596061.21311725</v>
       </c>
       <c r="Q16" t="n">
-        <v>-19100409.08687521</v>
+        <v>-23596061.21311725</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J17" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M17" t="n">
         <v>0.03830470017405307</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="P17" t="n">
-        <v>-16131024.30343279</v>
+        <v>-16675221.86723472</v>
       </c>
       <c r="Q17" t="n">
-        <v>-16131024.30343279</v>
+        <v>-16675221.86723472</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I18" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J18" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K18" t="n">
         <v>-124000000</v>
       </c>
       <c r="L18" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="M18" t="n">
         <v>0.03852218097221538</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="P18" t="n">
-        <v>-23441330.32639927</v>
+        <v>-17606803.4123548</v>
       </c>
       <c r="Q18" t="n">
-        <v>-23441330.32639927</v>
+        <v>-17606803.4123548</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I19" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J19" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K19" t="n">
         <v>-62000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="M19" t="n">
         <v>0.03873510939427094</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="P19" t="n">
-        <v>4582366.385962811</v>
+        <v>7922939.679442667</v>
       </c>
       <c r="Q19" t="n">
-        <v>2291183.192981406</v>
+        <v>3961469.839721334</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I20" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J20" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K20" t="n">
         <v>-62000000</v>
       </c>
       <c r="L20" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="M20" t="n">
         <v>0.03888939094511485</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="P20" t="n">
-        <v>4119986.885892807</v>
+        <v>4738295.664215015</v>
       </c>
       <c r="Q20" t="n">
-        <v>2059993.442946403</v>
+        <v>2369147.832107508</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J21" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K21" t="n">
         <v>-31000000</v>
       </c>
       <c r="L21" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="M21" t="n">
         <v>0.03901400018340251</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="P21" t="n">
-        <v>-1051738.605854207</v>
+        <v>-3022952.39708694</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1051738.605854207</v>
+        <v>-3022952.39708694</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I22" t="n">
         <v>2250000</v>
       </c>
       <c r="J22" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K22" t="n">
         <v>-31000000</v>
       </c>
       <c r="L22" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="M22" t="n">
         <v>0.03908855826627113</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="P22" t="n">
-        <v>190665.3809258619</v>
+        <v>-962775.3326304983</v>
       </c>
       <c r="Q22" t="n">
-        <v>95332.69046293097</v>
+        <v>-962775.3326304983</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I23" t="n">
         <v>2250000</v>
       </c>
       <c r="J23" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K23" t="n">
         <v>-31000000</v>
       </c>
       <c r="L23" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="M23" t="n">
         <v>0.03915884386251234</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="P23" t="n">
-        <v>-110207.7521488922</v>
+        <v>-128465.5126474221</v>
       </c>
       <c r="Q23" t="n">
-        <v>-110207.7521488922</v>
+        <v>-128465.5126474221</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I24" t="n">
         <v>2250000</v>
       </c>
       <c r="J24" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K24" t="n">
         <v>-31000000</v>
       </c>
       <c r="L24" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="M24" t="n">
         <v>0.03922681220647117</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="P24" t="n">
-        <v>-76368.57196996707</v>
+        <v>-72085.94084145165</v>
       </c>
       <c r="Q24" t="n">
-        <v>-76368.57196996707</v>
+        <v>-72085.94084145165</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I25" t="n">
         <v>2250000</v>
       </c>
       <c r="J25" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K25" t="n">
         <v>-31000000</v>
       </c>
       <c r="L25" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="M25" t="n">
         <v>0.03929424848359133</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="P25" t="n">
-        <v>-60301.13856132274</v>
+        <v>-54227.95752525954</v>
       </c>
       <c r="Q25" t="n">
-        <v>-60301.13856132274</v>
+        <v>-54227.95752525954</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J26" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M26" t="n">
         <v>0.03936107056455495</v>
@@ -2974,10 +2974,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="P26" t="n">
-        <v>-80987.4201389782</v>
+        <v>-264876.8690425178</v>
       </c>
       <c r="Q26" t="n">
-        <v>-80987.4201389782</v>
+        <v>-264876.8690425178</v>
       </c>
     </row>
     <row r="27">
@@ -3011,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J27" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K27" t="n">
         <v>-62000000</v>
       </c>
       <c r="L27" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="M27" t="n">
         <v>0.03942868733737526</v>
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K28" t="n">
         <v>-620000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="M28" t="n">
         <v>0.03432749872940843</v>
@@ -3096,10 +3096,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="P28" t="n">
-        <v>15553292.57838485</v>
+        <v>15101057.508424</v>
       </c>
       <c r="Q28" t="n">
-        <v>7776646.289192423</v>
+        <v>7550528.754212001</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J29" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K29" t="n">
         <v>-62000000</v>
       </c>
       <c r="L29" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="M29" t="n">
         <v>0.03782665436246635</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="P29" t="n">
-        <v>-15141069.48101515</v>
+        <v>-18704814.15770261</v>
       </c>
       <c r="Q29" t="n">
-        <v>-15141069.48101515</v>
+        <v>-18704814.15770261</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J30" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M30" t="n">
         <v>0.03830470017405307</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="P30" t="n">
-        <v>-11065882.21964725</v>
+        <v>-11439201.73314953</v>
       </c>
       <c r="Q30" t="n">
-        <v>-11065882.21964725</v>
+        <v>-11439201.73314953</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I31" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J31" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K31" t="n">
         <v>-124000000</v>
       </c>
       <c r="L31" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="M31" t="n">
         <v>0.03852218097221538</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="P31" t="n">
-        <v>-13816048.55110825</v>
+        <v>-10377245.97485666</v>
       </c>
       <c r="Q31" t="n">
-        <v>-13816048.55110825</v>
+        <v>-10377245.97485666</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I32" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J32" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K32" t="n">
         <v>-62000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="M32" t="n">
         <v>0.03873510939427094</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="P32" t="n">
-        <v>2290536.840539652</v>
+        <v>3960352.292372139</v>
       </c>
       <c r="Q32" t="n">
-        <v>1145268.420269826</v>
+        <v>1980176.14618607</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I33" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J33" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K33" t="n">
         <v>-62000000</v>
       </c>
       <c r="L33" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="M33" t="n">
         <v>0.03888939094511485</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="P33" t="n">
-        <v>1717240.814220452</v>
+        <v>1974956.457336046</v>
       </c>
       <c r="Q33" t="n">
-        <v>858620.4071102258</v>
+        <v>987478.2286680231</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J34" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K34" t="n">
         <v>-31000000</v>
       </c>
       <c r="L34" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="M34" t="n">
         <v>0.03901400018340251</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="P34" t="n">
-        <v>-358383.9370935452</v>
+        <v>-1030082.546826817</v>
       </c>
       <c r="Q34" t="n">
-        <v>-358383.9370935452</v>
+        <v>-1030082.546826817</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I35" t="n">
         <v>2250000</v>
       </c>
       <c r="J35" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K35" t="n">
         <v>-31000000</v>
       </c>
       <c r="L35" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="M35" t="n">
         <v>0.03908855826627113</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="P35" t="n">
-        <v>51456.925574181</v>
+        <v>-259834.5771804717</v>
       </c>
       <c r="Q35" t="n">
-        <v>25728.4627870905</v>
+        <v>-259834.5771804717</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I36" t="n">
         <v>2250000</v>
       </c>
       <c r="J36" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K36" t="n">
         <v>-31000000</v>
       </c>
       <c r="L36" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="M36" t="n">
         <v>0.03915884386251234</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="P36" t="n">
-        <v>-22672.88196456904</v>
+        <v>-26429.02470996576</v>
       </c>
       <c r="Q36" t="n">
-        <v>-22672.88196456904</v>
+        <v>-26429.02470996576</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I37" t="n">
         <v>2250000</v>
       </c>
       <c r="J37" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K37" t="n">
         <v>-31000000</v>
       </c>
       <c r="L37" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="M37" t="n">
         <v>0.03922681220647117</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="P37" t="n">
-        <v>-11147.72795242223</v>
+        <v>-10522.58065020424</v>
       </c>
       <c r="Q37" t="n">
-        <v>-11147.72795242223</v>
+        <v>-10522.58065020424</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I38" t="n">
         <v>2250000</v>
       </c>
       <c r="J38" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K38" t="n">
         <v>-31000000</v>
       </c>
       <c r="L38" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="M38" t="n">
         <v>0.03929424848359133</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="P38" t="n">
-        <v>-5486.505123349388</v>
+        <v>-4933.936139340835</v>
       </c>
       <c r="Q38" t="n">
-        <v>-5486.505123349388</v>
+        <v>-4933.936139340835</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J39" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M39" t="n">
         <v>0.03936107056455495</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="P39" t="n">
-        <v>-3256.01209752836</v>
+        <v>-10649.08955585796</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3256.01209752836</v>
+        <v>-10649.08955585796</v>
       </c>
     </row>
     <row r="40">
@@ -3804,19 +3804,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J40" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K40" t="n">
         <v>-62000000</v>
       </c>
       <c r="L40" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="M40" t="n">
         <v>0.03942868733737526</v>
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K41" t="n">
         <v>-620000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="M41" t="n">
         <v>0.03432749872940843</v>
@@ -3889,10 +3889,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="P41" t="n">
-        <v>-36400113.47886805</v>
+        <v>-35843183.64759321</v>
       </c>
       <c r="Q41" t="n">
-        <v>-36400113.47886805</v>
+        <v>-35843183.64759321</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J42" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K42" t="n">
         <v>-62000000</v>
       </c>
       <c r="L42" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="M42" t="n">
         <v>0.03782665436246635</v>
@@ -3950,10 +3950,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="P42" t="n">
-        <v>17587520.64685568</v>
+        <v>22060508.68372681</v>
       </c>
       <c r="Q42" t="n">
-        <v>8793760.323427841</v>
+        <v>11030254.3418634</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J43" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M43" t="n">
         <v>0.03830470017405307</v>
@@ -4011,10 +4011,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="P43" t="n">
-        <v>14203608.38506325</v>
+        <v>14682782.48677873</v>
       </c>
       <c r="Q43" t="n">
-        <v>7101804.192531625</v>
+        <v>7341391.243389367</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I44" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J44" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K44" t="n">
         <v>-124000000</v>
       </c>
       <c r="L44" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="M44" t="n">
         <v>0.03852218097221538</v>
@@ -4072,10 +4072,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="P44" t="n">
-        <v>16382250.36081849</v>
+        <v>11852544.88539599</v>
       </c>
       <c r="Q44" t="n">
-        <v>8191125.180409247</v>
+        <v>5926272.442697996</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I45" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J45" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K45" t="n">
         <v>-62000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="M45" t="n">
         <v>0.03873510939427094</v>
@@ -4133,10 +4133,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="P45" t="n">
-        <v>-3822103.415648551</v>
+        <v>-6092099.392468265</v>
       </c>
       <c r="Q45" t="n">
-        <v>-3822103.415648551</v>
+        <v>-6092099.392468265</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I46" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J46" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K46" t="n">
         <v>-62000000</v>
       </c>
       <c r="L46" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="M46" t="n">
         <v>0.03888939094511485</v>
@@ -4194,10 +4194,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="P46" t="n">
-        <v>-2967529.679335522</v>
+        <v>-3332019.392963285</v>
       </c>
       <c r="Q46" t="n">
-        <v>-2967529.679335522</v>
+        <v>-3332019.392963285</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J47" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K47" t="n">
         <v>-31000000</v>
       </c>
       <c r="L47" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="M47" t="n">
         <v>0.03901400018340251</v>
@@ -4255,10 +4255,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="P47" t="n">
-        <v>334098.562381001</v>
+        <v>1333247.680821666</v>
       </c>
       <c r="Q47" t="n">
-        <v>167049.2811905005</v>
+        <v>666623.8404108328</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I48" t="n">
         <v>2250000</v>
       </c>
       <c r="J48" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K48" t="n">
         <v>-31000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="M48" t="n">
         <v>0.03908855826627113</v>
@@ -4316,10 +4316,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="P48" t="n">
-        <v>-222903.7581030664</v>
+        <v>272926.0770663384</v>
       </c>
       <c r="Q48" t="n">
-        <v>-222903.7581030664</v>
+        <v>136463.0385331692</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I49" t="n">
         <v>2250000</v>
       </c>
       <c r="J49" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K49" t="n">
         <v>-31000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="M49" t="n">
         <v>0.03915884386251234</v>
@@ -4377,10 +4377,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="P49" t="n">
-        <v>-54965.74260521386</v>
+        <v>-48392.47326003701</v>
       </c>
       <c r="Q49" t="n">
-        <v>-54965.74260521386</v>
+        <v>-48392.47326003701</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I50" t="n">
         <v>2250000</v>
       </c>
       <c r="J50" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K50" t="n">
         <v>-31000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="M50" t="n">
         <v>0.03922681220647117</v>
@@ -4438,10 +4438,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="P50" t="n">
-        <v>-35766.3135039513</v>
+        <v>-37029.89819425395</v>
       </c>
       <c r="Q50" t="n">
-        <v>-35766.3135039513</v>
+        <v>-37029.89819425395</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I51" t="n">
         <v>2250000</v>
       </c>
       <c r="J51" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K51" t="n">
         <v>-31000000</v>
       </c>
       <c r="L51" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="M51" t="n">
         <v>0.03929424848359133</v>
@@ -4499,10 +4499,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="P51" t="n">
-        <v>-16873.10949510173</v>
+        <v>-18302.01192023674</v>
       </c>
       <c r="Q51" t="n">
-        <v>-16873.10949510173</v>
+        <v>-18302.01192023674</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J52" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M52" t="n">
         <v>0.03936107056455495</v>
@@ -4560,10 +4560,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="P52" t="n">
-        <v>14590.67331600027</v>
+        <v>47720.15034597104</v>
       </c>
       <c r="Q52" t="n">
-        <v>7295.336658000136</v>
+        <v>23860.07517298552</v>
       </c>
     </row>
     <row r="53">
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J53" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K53" t="n">
         <v>-62000000</v>
       </c>
       <c r="L53" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="M53" t="n">
         <v>0.03942868733737526</v>
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K54" t="n">
         <v>-620000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="M54" t="n">
         <v>0.03432749872940843</v>
@@ -4682,10 +4682,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="P54" t="n">
-        <v>-45555412.33908088</v>
+        <v>-44858404.39919109</v>
       </c>
       <c r="Q54" t="n">
-        <v>-45555412.33908088</v>
+        <v>-44858404.39919109</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J55" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K55" t="n">
         <v>-62000000</v>
       </c>
       <c r="L55" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="M55" t="n">
         <v>0.03782665436246635</v>
@@ -4743,10 +4743,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="P55" t="n">
-        <v>22798350.35485325</v>
+        <v>28596595.05604066</v>
       </c>
       <c r="Q55" t="n">
-        <v>11399175.17742662</v>
+        <v>14298297.52802033</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J56" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M56" t="n">
         <v>0.03830470017405307</v>
@@ -4804,10 +4804,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="P56" t="n">
-        <v>19176609.28310079</v>
+        <v>19823552.95248848</v>
       </c>
       <c r="Q56" t="n">
-        <v>9588304.641550394</v>
+        <v>9911776.476244241</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I57" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J57" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K57" t="n">
         <v>-124000000</v>
       </c>
       <c r="L57" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="M57" t="n">
         <v>0.03852218097221538</v>
@@ -4865,10 +4865,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="P57" t="n">
-        <v>23145956.52644055</v>
+        <v>16746080.82545226</v>
       </c>
       <c r="Q57" t="n">
-        <v>11572978.26322027</v>
+        <v>8373040.41272613</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I58" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J58" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K58" t="n">
         <v>-62000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="M58" t="n">
         <v>0.03873510939427094</v>
@@ -4926,10 +4926,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="P58" t="n">
-        <v>-5688889.861039254</v>
+        <v>-9067594.122221133</v>
       </c>
       <c r="Q58" t="n">
-        <v>-5688889.861039254</v>
+        <v>-9067594.122221133</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I59" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J59" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K59" t="n">
         <v>-62000000</v>
       </c>
       <c r="L59" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="M59" t="n">
         <v>0.03888939094511485</v>
@@ -4987,10 +4987,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="P59" t="n">
-        <v>-4691259.720509267</v>
+        <v>-5267468.249774846</v>
       </c>
       <c r="Q59" t="n">
-        <v>-4691259.720509267</v>
+        <v>-5267468.249774846</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J60" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K60" t="n">
         <v>-31000000</v>
       </c>
       <c r="L60" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="M60" t="n">
         <v>0.03901400018340251</v>
@@ -5048,10 +5048,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="P60" t="n">
-        <v>566141.6862732342</v>
+        <v>2259234.774495934</v>
       </c>
       <c r="Q60" t="n">
-        <v>283070.8431366171</v>
+        <v>1129617.387247967</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I61" t="n">
         <v>2250000</v>
       </c>
       <c r="J61" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K61" t="n">
         <v>-31000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="M61" t="n">
         <v>0.03908855826627113</v>
@@ -5109,10 +5109,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="P61" t="n">
-        <v>-410087.2692329567</v>
+        <v>502115.8485575956</v>
       </c>
       <c r="Q61" t="n">
-        <v>-410087.2692329567</v>
+        <v>251057.9242787978</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I62" t="n">
         <v>2250000</v>
       </c>
       <c r="J62" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K62" t="n">
         <v>-31000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="M62" t="n">
         <v>0.03915884386251234</v>
@@ -5170,10 +5170,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="P62" t="n">
-        <v>-111309.5548267598</v>
+        <v>-97998.21489229999</v>
       </c>
       <c r="Q62" t="n">
-        <v>-111309.5548267598</v>
+        <v>-97998.21489229999</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I63" t="n">
         <v>2250000</v>
       </c>
       <c r="J63" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K63" t="n">
         <v>-31000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="M63" t="n">
         <v>0.03922681220647117</v>
@@ -5231,10 +5231,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="P63" t="n">
-        <v>-81411.18212421431</v>
+        <v>-84287.3500395974</v>
       </c>
       <c r="Q63" t="n">
-        <v>-81411.18212421431</v>
+        <v>-84287.3500395974</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I64" t="n">
         <v>2250000</v>
       </c>
       <c r="J64" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K64" t="n">
         <v>-31000000</v>
       </c>
       <c r="L64" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="M64" t="n">
         <v>0.03929424848359133</v>
@@ -5292,10 +5292,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="P64" t="n">
-        <v>-44368.47884161649</v>
+        <v>-48125.83174890021</v>
       </c>
       <c r="Q64" t="n">
-        <v>-44368.47884161649</v>
+        <v>-48125.83174890021</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J65" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M65" t="n">
         <v>0.03936107056455495</v>
@@ -5353,10 +5353,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="P65" t="n">
-        <v>46151.69024950127</v>
+        <v>150943.3834702989</v>
       </c>
       <c r="Q65" t="n">
-        <v>23075.84512475063</v>
+        <v>75471.69173514945</v>
       </c>
     </row>
     <row r="66">
@@ -5390,19 +5390,19 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J66" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K66" t="n">
         <v>-62000000</v>
       </c>
       <c r="L66" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="M66" t="n">
         <v>0.03942868733737526</v>
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K67" t="n">
         <v>-620000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="M67" t="n">
         <v>0.03432749872940843</v>
@@ -5475,10 +5475,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="P67" t="n">
-        <v>23569984.80586207</v>
+        <v>22884652.50892653</v>
       </c>
       <c r="Q67" t="n">
-        <v>11784992.40293104</v>
+        <v>11442326.25446326</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J68" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K68" t="n">
         <v>-62000000</v>
       </c>
       <c r="L68" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="M68" t="n">
         <v>0.03782665436246635</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="P68" t="n">
-        <v>-24567358.5858387</v>
+        <v>-30349763.42126547</v>
       </c>
       <c r="Q68" t="n">
-        <v>-24567358.5858387</v>
+        <v>-30349763.42126547</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J69" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M69" t="n">
         <v>0.03830470017405307</v>
@@ -5597,10 +5597,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="P69" t="n">
-        <v>-19080794.85522814</v>
+        <v>-19724506.12118971</v>
       </c>
       <c r="Q69" t="n">
-        <v>-19080794.85522814</v>
+        <v>-19724506.12118971</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I70" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J70" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K70" t="n">
         <v>-124000000</v>
       </c>
       <c r="L70" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="M70" t="n">
         <v>0.03852218097221538</v>
@@ -5658,10 +5658,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="P70" t="n">
-        <v>-25537359.96755828</v>
+        <v>-19181133.08240744</v>
       </c>
       <c r="Q70" t="n">
-        <v>-25537359.96755828</v>
+        <v>-19181133.08240744</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I71" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J71" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K71" t="n">
         <v>-62000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="M71" t="n">
         <v>0.03873510939427094</v>
@@ -5719,10 +5719,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="P71" t="n">
-        <v>4596046.984955874</v>
+        <v>7946593.519286795</v>
       </c>
       <c r="Q71" t="n">
-        <v>2298023.492477937</v>
+        <v>3973296.759643397</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I72" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J72" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K72" t="n">
         <v>-62000000</v>
       </c>
       <c r="L72" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="M72" t="n">
         <v>0.03888939094511485</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="P72" t="n">
-        <v>3802626.404550575</v>
+        <v>4373307.174109367</v>
       </c>
       <c r="Q72" t="n">
-        <v>1901313.202275287</v>
+        <v>2186653.587054683</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J73" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K73" t="n">
         <v>-31000000</v>
       </c>
       <c r="L73" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="M73" t="n">
         <v>0.03901400018340251</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="P73" t="n">
-        <v>-893800.6483026487</v>
+        <v>-2569000.317440942</v>
       </c>
       <c r="Q73" t="n">
-        <v>-893800.6483026487</v>
+        <v>-2569000.317440942</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I74" t="n">
         <v>2250000</v>
       </c>
       <c r="J74" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K74" t="n">
         <v>-31000000</v>
       </c>
       <c r="L74" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="M74" t="n">
         <v>0.03908855826627113</v>
@@ -5902,10 +5902,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="P74" t="n">
-        <v>149068.6815115365</v>
+        <v>-752730.5100177852</v>
       </c>
       <c r="Q74" t="n">
-        <v>74534.34075576825</v>
+        <v>-752730.5100177852</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I75" t="n">
         <v>2250000</v>
       </c>
       <c r="J75" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K75" t="n">
         <v>-31000000</v>
       </c>
       <c r="L75" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="M75" t="n">
         <v>0.03915884386251234</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="P75" t="n">
-        <v>-79392.33839806204</v>
+        <v>-92545.00934567132</v>
       </c>
       <c r="Q75" t="n">
-        <v>-79392.33839806204</v>
+        <v>-92545.00934567132</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I76" t="n">
         <v>2250000</v>
       </c>
       <c r="J76" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K76" t="n">
         <v>-31000000</v>
       </c>
       <c r="L76" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="M76" t="n">
         <v>0.03922681220647117</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="P76" t="n">
-        <v>-50655.0529587973</v>
+        <v>-47814.39611499438</v>
       </c>
       <c r="Q76" t="n">
-        <v>-50655.0529587973</v>
+        <v>-47814.39611499438</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I77" t="n">
         <v>2250000</v>
       </c>
       <c r="J77" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K77" t="n">
         <v>-31000000</v>
       </c>
       <c r="L77" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="M77" t="n">
         <v>0.03929424848359133</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="P77" t="n">
-        <v>-36836.82866670786</v>
+        <v>-33126.83687177927</v>
       </c>
       <c r="Q77" t="n">
-        <v>-36836.82866670786</v>
+        <v>-33126.83687177927</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J78" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M78" t="n">
         <v>0.03936107056455495</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="P78" t="n">
-        <v>-45563.22508157478</v>
+        <v>-149018.7535592156</v>
       </c>
       <c r="Q78" t="n">
-        <v>-45563.22508157478</v>
+        <v>-149018.7535592156</v>
       </c>
     </row>
     <row r="79">
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J79" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K79" t="n">
         <v>-62000000</v>
       </c>
       <c r="L79" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="M79" t="n">
         <v>0.03942868733737526</v>
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="K80" t="n">
         <v>-620000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="M80" t="n">
         <v>0.03432749872940843</v>
@@ -6268,10 +6268,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="P80" t="n">
-        <v>6867988.405351218</v>
+        <v>6668291.447209972</v>
       </c>
       <c r="Q80" t="n">
-        <v>3433994.202675609</v>
+        <v>3334145.723604986</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="I81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J81" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="K81" t="n">
         <v>-62000000</v>
       </c>
       <c r="L81" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="M81" t="n">
         <v>0.03782665436246635</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="P81" t="n">
-        <v>-7644554.915038845</v>
+        <v>-9443849.338611366</v>
       </c>
       <c r="Q81" t="n">
-        <v>-7644554.915038845</v>
+        <v>-9443849.338611366</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="I82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J82" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="M82" t="n">
         <v>0.03830470017405307</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="P82" t="n">
-        <v>-6460035.001773206</v>
+        <v>-6677971.274381265</v>
       </c>
       <c r="Q82" t="n">
-        <v>-6460035.001773206</v>
+        <v>-6677971.274381265</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="I83" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="J83" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="K83" t="n">
         <v>-124000000</v>
       </c>
       <c r="L83" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="M83" t="n">
         <v>0.03852218097221538</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="P83" t="n">
-        <v>-9393847.739824571</v>
+        <v>-7055727.133985166</v>
       </c>
       <c r="Q83" t="n">
-        <v>-9393847.739824571</v>
+        <v>-7055727.133985166</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="I84" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="J84" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="K84" t="n">
         <v>-62000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="M84" t="n">
         <v>0.03873510939427094</v>
@@ -6512,10 +6512,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="P84" t="n">
-        <v>1837515.243005143</v>
+        <v>3177075.162515025</v>
       </c>
       <c r="Q84" t="n">
-        <v>918757.6215025715</v>
+        <v>1588537.581257512</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="I85" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="J85" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="K85" t="n">
         <v>-62000000</v>
       </c>
       <c r="L85" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="M85" t="n">
         <v>0.03888939094511485</v>
@@ -6573,10 +6573,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="P85" t="n">
-        <v>1653115.894634848</v>
+        <v>1901207.963261712</v>
       </c>
       <c r="Q85" t="n">
-        <v>826557.9473174242</v>
+        <v>950603.9816308562</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="I86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J86" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="K86" t="n">
         <v>-31000000</v>
       </c>
       <c r="L86" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="M86" t="n">
         <v>0.03901400018340251</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="P86" t="n">
-        <v>-422270.4852867442</v>
+        <v>-1213708.015101215</v>
       </c>
       <c r="Q86" t="n">
-        <v>-422270.4852867442</v>
+        <v>-1213708.015101215</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="I87" t="n">
         <v>2250000</v>
       </c>
       <c r="J87" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="K87" t="n">
         <v>-31000000</v>
       </c>
       <c r="L87" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="M87" t="n">
         <v>0.03908855826627113</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="P87" t="n">
-        <v>76596.03050434779</v>
+        <v>-386775.870841881</v>
       </c>
       <c r="Q87" t="n">
-        <v>38298.01525217389</v>
+        <v>-386775.870841881</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="I88" t="n">
         <v>2250000</v>
       </c>
       <c r="J88" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="K88" t="n">
         <v>-31000000</v>
       </c>
       <c r="L88" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="M88" t="n">
         <v>0.03915884386251234</v>
@@ -6756,10 +6756,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="P88" t="n">
-        <v>-44303.36437051645</v>
+        <v>-51642.95891068261</v>
       </c>
       <c r="Q88" t="n">
-        <v>-44303.36437051645</v>
+        <v>-51642.95891068261</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="I89" t="n">
         <v>2250000</v>
       </c>
       <c r="J89" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="K89" t="n">
         <v>-31000000</v>
       </c>
       <c r="L89" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="M89" t="n">
         <v>0.03922681220647117</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="P89" t="n">
-        <v>-30718.96594329398</v>
+        <v>-28996.29395413733</v>
       </c>
       <c r="Q89" t="n">
-        <v>-30718.96594329398</v>
+        <v>-28996.29395413733</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="I90" t="n">
         <v>2250000</v>
       </c>
       <c r="J90" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="K90" t="n">
         <v>-31000000</v>
       </c>
       <c r="L90" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="M90" t="n">
         <v>0.03929424848359133</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="P90" t="n">
-        <v>-24271.18800634034</v>
+        <v>-21826.73468025712</v>
       </c>
       <c r="Q90" t="n">
-        <v>-24271.18800634034</v>
+        <v>-21826.73468025712</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="I91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J91" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="M91" t="n">
         <v>0.03936107056455495</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="P91" t="n">
-        <v>-32617.79604745581</v>
+        <v>-106679.5272314068</v>
       </c>
       <c r="Q91" t="n">
-        <v>-32617.79604745581</v>
+        <v>-106679.5272314068</v>
       </c>
     </row>
     <row r="92">
@@ -6976,19 +6976,19 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="I92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J92" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="K92" t="n">
         <v>-62000000</v>
       </c>
       <c r="L92" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="M92" t="n">
         <v>0.03942868733737526</v>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35717002.64000005</v>
+        <v>33974881.98000002</v>
       </c>
       <c r="D2" t="n">
-        <v>17858501.32000002</v>
+        <v>16987440.99000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.97641688666667</v>
+        <v>2.831240165000002</v>
       </c>
       <c r="F2" t="n">
-        <v>1.488208443333335</v>
+        <v>1.415620082500001</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-39402456.87</v>
+        <v>-37559746.46999997</v>
       </c>
       <c r="D3" t="n">
-        <v>-39402456.87</v>
+        <v>-37559746.46999997</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.2835380725</v>
+        <v>-3.129978872499997</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2835380725</v>
+        <v>-3.129978872499997</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24954858.69</v>
+        <v>24824503.67000002</v>
       </c>
       <c r="D4" t="n">
-        <v>12477429.345</v>
+        <v>12412251.83500001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0795715575</v>
+        <v>2.068708639166668</v>
       </c>
       <c r="F4" t="n">
-        <v>1.03978577875</v>
+        <v>1.034354319583334</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-25784012.27999997</v>
+        <v>-25774751.25999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-25784012.27999997</v>
+        <v>-25774751.25999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.148667689999998</v>
+        <v>-2.147895938333332</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.148667689999998</v>
+        <v>-2.147895938333332</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-8155775.48999995</v>
+        <v>-8859880.549999952</v>
       </c>
       <c r="D6" t="n">
-        <v>-8155775.48999995</v>
+        <v>-8859880.549999952</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6796479574999958</v>
+        <v>-0.7383233791666627</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6796479574999958</v>
+        <v>-0.7383233791666627</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4659880.629999995</v>
+        <v>5485240.069999993</v>
       </c>
       <c r="D7" t="n">
-        <v>2329940.314999998</v>
+        <v>2742620.034999996</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3883233858333329</v>
+        <v>0.4571033391666661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1941616929166665</v>
+        <v>0.228551669583333</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-16848137.46999997</v>
+        <v>-16078052.23999995</v>
       </c>
       <c r="D8" t="n">
-        <v>-16848137.46999997</v>
+        <v>-16078052.23999995</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.404011455833331</v>
+        <v>-1.339837686666663</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.404011455833331</v>
+        <v>-1.339837686666663</v>
       </c>
     </row>
   </sheetData>
